--- a/summer-homework/四年级暑假作业计划表.xlsx
+++ b/summer-homework/四年级暑假作业计划表.xlsx
@@ -120,7 +120,7 @@
       <sz val="10.5"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -190,11 +190,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F4B183"/>
       </patternFill>
     </fill>
     <fill>
@@ -344,7 +339,7 @@
     <xf numFmtId="0" fontId="10" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -356,7 +351,7 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -407,12 +402,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -885,7 +880,7 @@
       </c>
       <c r="D6" s="5" t="n"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="62" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
           <t>实践</t>
@@ -1029,7 +1024,7 @@
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>英语视听练习,一个英文动画电影或BBC纪录片,内容自选,共计2天,每次不超过10分钟</t>
+          <t>英语试听练习,一个英文动画电影或BBC记录片,内容自选,共计2天,每次不超过10分钟</t>
         </is>
       </c>
       <c r="C15" s="13" t="inlineStr">
@@ -1111,7 +1106,7 @@
       </c>
       <c r="B20" s="19" t="inlineStr">
         <is>
-          <t>①准备热身活动 ②跳绳200个/组×4组 ③一分钟仰卧起坐2组,并记录成绩 ④坐位体前屈拉伸1分钟</t>
+          <t>①准备热身活动 ②跳绳200个/组×4组 ③一分钟仰卧起坐2组,并记录成绩 ④坐位体前屈拉伸,膝盖伸直,手触脚尖1分钟</t>
         </is>
       </c>
       <c r="C20" s="19" t="inlineStr">
@@ -1458,7 +1453,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1484,14 +1479,14 @@
     <col width="22" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="58.2" customHeight="1">
       <c r="A1" s="27" t="inlineStr">
         <is>
           <t>四年级暑假每日安排 · 第1周(7月13日—7月19日)    完成一项在□里打✓</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="58.2" customHeight="1">
       <c r="A2" s="28" t="inlineStr">
         <is>
           <t>科目</t>
@@ -1550,7 +1545,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1">
+    <row r="3" ht="46.6" customHeight="1">
       <c r="A3" s="30" t="inlineStr">
         <is>
           <t>数学</t>
@@ -1602,7 +1597,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1">
+    <row r="4" ht="46.6" customHeight="1">
       <c r="A4" s="3" t="n"/>
       <c r="B4" s="31" t="inlineStr">
         <is>
@@ -1650,7 +1645,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
+    <row r="5" ht="54.3" customHeight="1">
       <c r="A5" s="3" t="n"/>
       <c r="B5" s="31" t="inlineStr">
         <is>
@@ -1698,7 +1693,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="1">
+    <row r="6" ht="38.8" customHeight="1">
       <c r="A6" s="3" t="n"/>
       <c r="B6" s="31" t="inlineStr">
         <is>
@@ -1722,7 +1717,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="24" customHeight="1">
+    <row r="7" ht="46.6" customHeight="1">
       <c r="A7" s="35" t="inlineStr">
         <is>
           <t>英语</t>
@@ -1774,7 +1769,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="24" customHeight="1">
+    <row r="8" ht="46.6" customHeight="1">
       <c r="A8" s="9" t="n"/>
       <c r="B8" s="36" t="inlineStr">
         <is>
@@ -1822,7 +1817,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="24" customHeight="1">
+    <row r="9" ht="46.6" customHeight="1">
       <c r="A9" s="9" t="n"/>
       <c r="B9" s="36" t="inlineStr">
         <is>
@@ -1870,7 +1865,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="96" customHeight="1">
+    <row r="10" ht="186.3" customHeight="1">
       <c r="A10" s="39" t="inlineStr">
         <is>
           <t>体育</t>
@@ -1919,7 +1914,8 @@
         <is>
           <t>□ 热身
 □ 耐力跑2公里
-(避开正午炎热,记录)
+(避开中午炎热时段,
+注意防暑降温,并记录)
 □ 放松拉伸</t>
         </is>
       </c>
@@ -1939,7 +1935,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="26" customHeight="1">
+    <row r="11" ht="50.4" customHeight="1">
       <c r="A11" s="15" t="n"/>
       <c r="B11" s="40" t="inlineStr">
         <is>
@@ -1987,7 +1983,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="26" customHeight="1">
+    <row r="12" ht="50.4" customHeight="1">
       <c r="A12" s="15" t="n"/>
       <c r="B12" s="43" t="inlineStr">
         <is>
@@ -2007,7 +2003,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="26" customHeight="1">
+    <row r="13" ht="50.4" customHeight="1">
       <c r="A13" s="45" t="inlineStr">
         <is>
           <t>★ 英语作业不含周六日和法定节假日 · 体育锻炼注意防暑降温 · 数学实践作业4选2(本表建议做③气温统计、④密铺图案,也可换成①数学游戏、②小区调查)</t>
@@ -2061,14 +2057,14 @@
     <col width="22" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="58.2" customHeight="1">
       <c r="A1" s="27" t="inlineStr">
         <is>
           <t>四年级暑假每日安排 · 第2周(7月20日—7月26日)    完成一项在□里打✓</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="58.2" customHeight="1">
       <c r="A2" s="28" t="inlineStr">
         <is>
           <t>科目</t>
@@ -2127,7 +2123,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1">
+    <row r="3" ht="46.6" customHeight="1">
       <c r="A3" s="30" t="inlineStr">
         <is>
           <t>数学</t>
@@ -2179,7 +2175,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1">
+    <row r="4" ht="46.6" customHeight="1">
       <c r="A4" s="3" t="n"/>
       <c r="B4" s="31" t="inlineStr">
         <is>
@@ -2227,7 +2223,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
+    <row r="5" ht="54.3" customHeight="1">
       <c r="A5" s="3" t="n"/>
       <c r="B5" s="31" t="inlineStr">
         <is>
@@ -2275,7 +2271,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="1">
+    <row r="6" ht="38.8" customHeight="1">
       <c r="A6" s="3" t="n"/>
       <c r="B6" s="31" t="inlineStr">
         <is>
@@ -2299,7 +2295,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="24" customHeight="1">
+    <row r="7" ht="46.6" customHeight="1">
       <c r="A7" s="35" t="inlineStr">
         <is>
           <t>英语</t>
@@ -2351,7 +2347,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="24" customHeight="1">
+    <row r="8" ht="46.6" customHeight="1">
       <c r="A8" s="9" t="n"/>
       <c r="B8" s="36" t="inlineStr">
         <is>
@@ -2399,7 +2395,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="24" customHeight="1">
+    <row r="9" ht="46.6" customHeight="1">
       <c r="A9" s="9" t="n"/>
       <c r="B9" s="36" t="inlineStr">
         <is>
@@ -2447,7 +2443,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="96" customHeight="1">
+    <row r="10" ht="186.3" customHeight="1">
       <c r="A10" s="39" t="inlineStr">
         <is>
           <t>体育</t>
@@ -2496,7 +2492,8 @@
         <is>
           <t>□ 热身
 □ 耐力跑2公里
-(避开正午炎热,记录)
+(避开中午炎热时段,
+注意防暑降温,并记录)
 □ 放松拉伸</t>
         </is>
       </c>
@@ -2516,7 +2513,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="26" customHeight="1">
+    <row r="11" ht="50.4" customHeight="1">
       <c r="A11" s="15" t="n"/>
       <c r="B11" s="40" t="inlineStr">
         <is>
@@ -2564,7 +2561,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="26" customHeight="1">
+    <row r="12" ht="50.4" customHeight="1">
       <c r="A12" s="15" t="n"/>
       <c r="B12" s="43" t="inlineStr">
         <is>
@@ -2584,7 +2581,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="26" customHeight="1">
+    <row r="13" ht="50.4" customHeight="1">
       <c r="A13" s="45" t="inlineStr">
         <is>
           <t>★ 英语作业不含周六日和法定节假日 · 体育锻炼注意防暑降温 · 数学实践作业4选2(本表建议做③气温统计、④密铺图案,也可换成①数学游戏、②小区调查)</t>
@@ -2638,14 +2635,14 @@
     <col width="22" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="58.2" customHeight="1">
       <c r="A1" s="27" t="inlineStr">
         <is>
           <t>四年级暑假每日安排 · 第3周(7月27日—8月2日)    完成一项在□里打✓</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="58.2" customHeight="1">
       <c r="A2" s="28" t="inlineStr">
         <is>
           <t>科目</t>
@@ -2704,7 +2701,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1">
+    <row r="3" ht="46.6" customHeight="1">
       <c r="A3" s="30" t="inlineStr">
         <is>
           <t>数学</t>
@@ -2756,7 +2753,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1">
+    <row r="4" ht="46.6" customHeight="1">
       <c r="A4" s="3" t="n"/>
       <c r="B4" s="31" t="inlineStr">
         <is>
@@ -2804,7 +2801,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
+    <row r="5" ht="54.3" customHeight="1">
       <c r="A5" s="3" t="n"/>
       <c r="B5" s="31" t="inlineStr">
         <is>
@@ -2852,7 +2849,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="1">
+    <row r="6" ht="38.8" customHeight="1">
       <c r="A6" s="3" t="n"/>
       <c r="B6" s="31" t="inlineStr">
         <is>
@@ -2876,7 +2873,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="24" customHeight="1">
+    <row r="7" ht="46.6" customHeight="1">
       <c r="A7" s="35" t="inlineStr">
         <is>
           <t>英语</t>
@@ -2928,7 +2925,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="24" customHeight="1">
+    <row r="8" ht="46.6" customHeight="1">
       <c r="A8" s="9" t="n"/>
       <c r="B8" s="36" t="inlineStr">
         <is>
@@ -2976,7 +2973,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="24" customHeight="1">
+    <row r="9" ht="46.6" customHeight="1">
       <c r="A9" s="9" t="n"/>
       <c r="B9" s="36" t="inlineStr">
         <is>
@@ -3024,7 +3021,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="96" customHeight="1">
+    <row r="10" ht="186.3" customHeight="1">
       <c r="A10" s="39" t="inlineStr">
         <is>
           <t>体育</t>
@@ -3073,7 +3070,8 @@
         <is>
           <t>□ 热身
 □ 耐力跑2公里
-(避开正午炎热,记录)
+(避开中午炎热时段,
+注意防暑降温,并记录)
 □ 放松拉伸</t>
         </is>
       </c>
@@ -3093,7 +3091,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="26" customHeight="1">
+    <row r="11" ht="50.4" customHeight="1">
       <c r="A11" s="15" t="n"/>
       <c r="B11" s="40" t="inlineStr">
         <is>
@@ -3141,7 +3139,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="26" customHeight="1">
+    <row r="12" ht="50.4" customHeight="1">
       <c r="A12" s="15" t="n"/>
       <c r="B12" s="43" t="inlineStr">
         <is>
@@ -3161,7 +3159,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="26" customHeight="1">
+    <row r="13" ht="50.4" customHeight="1">
       <c r="A13" s="45" t="inlineStr">
         <is>
           <t>★ 英语作业不含周六日和法定节假日 · 体育锻炼注意防暑降温 · 数学实践作业4选2(本表建议做③气温统计、④密铺图案,也可换成①数学游戏、②小区调查)</t>
@@ -3215,14 +3213,14 @@
     <col width="22" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="53.9" customHeight="1">
       <c r="A1" s="27" t="inlineStr">
         <is>
           <t>四年级暑假每日安排 · 第4周(8月3日—8月9日)    完成一项在□里打✓</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="53.9" customHeight="1">
       <c r="A2" s="28" t="inlineStr">
         <is>
           <t>科目</t>
@@ -3281,7 +3279,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1">
+    <row r="3" ht="43.1" customHeight="1">
       <c r="A3" s="30" t="inlineStr">
         <is>
           <t>数学</t>
@@ -3333,7 +3331,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1">
+    <row r="4" ht="43.1" customHeight="1">
       <c r="A4" s="3" t="n"/>
       <c r="B4" s="31" t="inlineStr">
         <is>
@@ -3381,7 +3379,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
+    <row r="5" ht="50.3" customHeight="1">
       <c r="A5" s="3" t="n"/>
       <c r="B5" s="31" t="inlineStr">
         <is>
@@ -3429,11 +3427,11 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="32" customHeight="1">
+    <row r="6" ht="57.5" customHeight="1">
       <c r="A6" s="3" t="n"/>
       <c r="B6" s="47" t="inlineStr">
         <is>
-          <t>实践作业①:统计一周(7天)气温</t>
+          <t>实践作业(原单第③项):统计一周(7天)气温</t>
         </is>
       </c>
       <c r="C6" s="48" t="inlineStr">
@@ -3477,7 +3475,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1">
+    <row r="7" ht="35.9" customHeight="1">
       <c r="A7" s="3" t="n"/>
       <c r="B7" s="31" t="inlineStr">
         <is>
@@ -3501,7 +3499,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="24" customHeight="1">
+    <row r="8" ht="43.1" customHeight="1">
       <c r="A8" s="35" t="inlineStr">
         <is>
           <t>英语</t>
@@ -3553,7 +3551,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="24" customHeight="1">
+    <row r="9" ht="43.1" customHeight="1">
       <c r="A9" s="9" t="n"/>
       <c r="B9" s="36" t="inlineStr">
         <is>
@@ -3601,7 +3599,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="24" customHeight="1">
+    <row r="10" ht="43.1" customHeight="1">
       <c r="A10" s="9" t="n"/>
       <c r="B10" s="36" t="inlineStr">
         <is>
@@ -3649,7 +3647,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="96" customHeight="1">
+    <row r="11" ht="172.5" customHeight="1">
       <c r="A11" s="39" t="inlineStr">
         <is>
           <t>体育</t>
@@ -3698,7 +3696,8 @@
         <is>
           <t>□ 热身
 □ 耐力跑2公里
-(避开正午炎热,记录)
+(避开中午炎热时段,
+注意防暑降温,并记录)
 □ 放松拉伸</t>
         </is>
       </c>
@@ -3718,7 +3717,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="26" customHeight="1">
+    <row r="12" ht="46.7" customHeight="1">
       <c r="A12" s="15" t="n"/>
       <c r="B12" s="40" t="inlineStr">
         <is>
@@ -3766,7 +3765,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="26" customHeight="1">
+    <row r="13" ht="46.7" customHeight="1">
       <c r="A13" s="15" t="n"/>
       <c r="B13" s="43" t="inlineStr">
         <is>
@@ -3786,7 +3785,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="26" customHeight="1">
+    <row r="14" ht="46.7" customHeight="1">
       <c r="A14" s="45" t="inlineStr">
         <is>
           <t>★ 英语作业不含周六日和法定节假日 · 体育锻炼注意防暑降温 · 数学实践作业4选2(本表建议做③气温统计、④密铺图案,也可换成①数学游戏、②小区调查)</t>
@@ -3840,14 +3839,14 @@
     <col width="22" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="54.9" customHeight="1">
       <c r="A1" s="27" t="inlineStr">
         <is>
           <t>四年级暑假每日安排 · 第5周(8月10日—8月16日)    完成一项在□里打✓</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="54.9" customHeight="1">
       <c r="A2" s="28" t="inlineStr">
         <is>
           <t>科目</t>
@@ -3906,7 +3905,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1">
+    <row r="3" ht="43.9" customHeight="1">
       <c r="A3" s="30" t="inlineStr">
         <is>
           <t>数学</t>
@@ -3958,7 +3957,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1">
+    <row r="4" ht="43.9" customHeight="1">
       <c r="A4" s="3" t="n"/>
       <c r="B4" s="31" t="inlineStr">
         <is>
@@ -4006,7 +4005,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
+    <row r="5" ht="51.3" customHeight="1">
       <c r="A5" s="3" t="n"/>
       <c r="B5" s="31" t="inlineStr">
         <is>
@@ -4054,7 +4053,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="1">
+    <row r="6" ht="36.6" customHeight="1">
       <c r="A6" s="3" t="n"/>
       <c r="B6" s="31" t="inlineStr">
         <is>
@@ -4078,7 +4077,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="24" customHeight="1">
+    <row r="7" ht="43.9" customHeight="1">
       <c r="A7" s="35" t="inlineStr">
         <is>
           <t>英语</t>
@@ -4130,7 +4129,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="24" customHeight="1">
+    <row r="8" ht="43.9" customHeight="1">
       <c r="A8" s="9" t="n"/>
       <c r="B8" s="36" t="inlineStr">
         <is>
@@ -4178,7 +4177,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="24" customHeight="1">
+    <row r="9" ht="43.9" customHeight="1">
       <c r="A9" s="9" t="n"/>
       <c r="B9" s="36" t="inlineStr">
         <is>
@@ -4226,7 +4225,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="24" customHeight="1">
+    <row r="10" ht="43.9" customHeight="1">
       <c r="A10" s="9" t="n"/>
       <c r="B10" s="36" t="inlineStr">
         <is>
@@ -4274,7 +4273,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="96" customHeight="1">
+    <row r="11" ht="175.8" customHeight="1">
       <c r="A11" s="39" t="inlineStr">
         <is>
           <t>体育</t>
@@ -4323,7 +4322,8 @@
         <is>
           <t>□ 热身
 □ 耐力跑2公里
-(避开正午炎热,记录)
+(避开中午炎热时段,
+注意防暑降温,并记录)
 □ 放松拉伸</t>
         </is>
       </c>
@@ -4343,7 +4343,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="26" customHeight="1">
+    <row r="12" ht="47.6" customHeight="1">
       <c r="A12" s="15" t="n"/>
       <c r="B12" s="40" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="26" customHeight="1">
+    <row r="13" ht="47.6" customHeight="1">
       <c r="A13" s="15" t="n"/>
       <c r="B13" s="43" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="26" customHeight="1">
+    <row r="14" ht="47.6" customHeight="1">
       <c r="A14" s="45" t="inlineStr">
         <is>
           <t>★ 英语作业不含周六日和法定节假日 · 体育锻炼注意防暑降温 · 数学实践作业4选2(本表建议做③气温统计、④密铺图案,也可换成①数学游戏、②小区调查)</t>
@@ -4465,14 +4465,14 @@
     <col width="22" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="54.4" customHeight="1">
       <c r="A1" s="27" t="inlineStr">
         <is>
           <t>四年级暑假每日安排 · 第6周(8月17日—8月23日)    完成一项在□里打✓</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="54.4" customHeight="1">
       <c r="A2" s="28" t="inlineStr">
         <is>
           <t>科目</t>
@@ -4531,7 +4531,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1">
+    <row r="3" ht="43.5" customHeight="1">
       <c r="A3" s="30" t="inlineStr">
         <is>
           <t>数学</t>
@@ -4583,7 +4583,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1">
+    <row r="4" ht="43.5" customHeight="1">
       <c r="A4" s="3" t="n"/>
       <c r="B4" s="31" t="inlineStr">
         <is>
@@ -4631,7 +4631,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
+    <row r="5" ht="50.8" customHeight="1">
       <c r="A5" s="3" t="n"/>
       <c r="B5" s="31" t="inlineStr">
         <is>
@@ -4679,11 +4679,11 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1">
+    <row r="6" ht="50.8" customHeight="1">
       <c r="A6" s="3" t="n"/>
       <c r="B6" s="47" t="inlineStr">
         <is>
-          <t>实践作业②:设计密铺图案</t>
+          <t>实践作业(原单第④项):设计密铺图案</t>
         </is>
       </c>
       <c r="C6" s="33" t="inlineStr">
@@ -4727,7 +4727,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1">
+    <row r="7" ht="36.3" customHeight="1">
       <c r="A7" s="3" t="n"/>
       <c r="B7" s="31" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="24" customHeight="1">
+    <row r="8" ht="43.5" customHeight="1">
       <c r="A8" s="35" t="inlineStr">
         <is>
           <t>英语</t>
@@ -4803,7 +4803,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="24" customHeight="1">
+    <row r="9" ht="43.5" customHeight="1">
       <c r="A9" s="9" t="n"/>
       <c r="B9" s="36" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="24" customHeight="1">
+    <row r="10" ht="43.5" customHeight="1">
       <c r="A10" s="9" t="n"/>
       <c r="B10" s="36" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="96" customHeight="1">
+    <row r="11" ht="174.1" customHeight="1">
       <c r="A11" s="39" t="inlineStr">
         <is>
           <t>体育</t>
@@ -4948,7 +4948,8 @@
         <is>
           <t>□ 热身
 □ 耐力跑2公里
-(避开正午炎热,记录)
+(避开中午炎热时段,
+注意防暑降温,并记录)
 □ 放松拉伸</t>
         </is>
       </c>
@@ -4968,7 +4969,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="26" customHeight="1">
+    <row r="12" ht="47.2" customHeight="1">
       <c r="A12" s="15" t="n"/>
       <c r="B12" s="40" t="inlineStr">
         <is>
@@ -5016,7 +5017,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="26" customHeight="1">
+    <row r="13" ht="47.2" customHeight="1">
       <c r="A13" s="15" t="n"/>
       <c r="B13" s="43" t="inlineStr">
         <is>
@@ -5036,7 +5037,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="26" customHeight="1">
+    <row r="14" ht="47.2" customHeight="1">
       <c r="A14" s="45" t="inlineStr">
         <is>
           <t>★ 英语作业不含周六日和法定节假日 · 体育锻炼注意防暑降温 · 数学实践作业4选2(本表建议做③气温统计、④密铺图案,也可换成①数学游戏、②小区调查)</t>
@@ -5090,14 +5091,14 @@
     <col width="22" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="60" customHeight="1">
       <c r="A1" s="27" t="inlineStr">
         <is>
           <t>四年级暑假每日安排 · 第7周(8月24日—8月30日)    完成一项在□里打✓</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="60" customHeight="1">
       <c r="A2" s="28" t="inlineStr">
         <is>
           <t>科目</t>
@@ -5156,7 +5157,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1">
+    <row r="3" ht="48" customHeight="1">
       <c r="A3" s="30" t="inlineStr">
         <is>
           <t>数学</t>
@@ -5208,7 +5209,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1">
+    <row r="4" ht="48" customHeight="1">
       <c r="A4" s="3" t="n"/>
       <c r="B4" s="31" t="inlineStr">
         <is>
@@ -5256,7 +5257,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
+    <row r="5" ht="56" customHeight="1">
       <c r="A5" s="3" t="n"/>
       <c r="B5" s="31" t="inlineStr">
         <is>
@@ -5304,7 +5305,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="3" t="n"/>
       <c r="B6" s="31" t="inlineStr">
         <is>
@@ -5328,7 +5329,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="68" customHeight="1">
       <c r="A7" s="35" t="inlineStr">
         <is>
           <t>英语</t>
@@ -5383,11 +5384,11 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="24" customHeight="1">
+    <row r="8" ht="48" customHeight="1">
       <c r="A8" s="9" t="n"/>
       <c r="B8" s="36" t="inlineStr">
         <is>
-          <t>选做② 英语视听:英文动画电影 / BBC纪录片(每次≤10分钟)</t>
+          <t>选做② 英语试听练习:英文动画电影 / BBC记录片(每次≤10分钟)</t>
         </is>
       </c>
       <c r="C8" s="33" t="inlineStr">
@@ -5431,7 +5432,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="96" customHeight="1">
+    <row r="9" ht="192" customHeight="1">
       <c r="A9" s="39" t="inlineStr">
         <is>
           <t>体育</t>
@@ -5480,7 +5481,8 @@
         <is>
           <t>□ 热身
 □ 耐力跑2公里
-(避开正午炎热,记录)
+(避开中午炎热时段,
+注意防暑降温,并记录)
 □ 放松拉伸</t>
         </is>
       </c>
@@ -5500,7 +5502,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="26" customHeight="1">
+    <row r="10" ht="52" customHeight="1">
       <c r="A10" s="15" t="n"/>
       <c r="B10" s="40" t="inlineStr">
         <is>
@@ -5548,7 +5550,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="26" customHeight="1">
+    <row r="11" ht="52" customHeight="1">
       <c r="A11" s="15" t="n"/>
       <c r="B11" s="43" t="inlineStr">
         <is>
@@ -5568,7 +5570,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="26" customHeight="1">
+    <row r="12" ht="52" customHeight="1">
       <c r="A12" s="45" t="inlineStr">
         <is>
           <t>★ 本周是体育任务单最后一周,周末把“注明”栏填好:跳绳最好成绩、跑步公里数及用时、仰卧起坐最好成绩 · 英语必做已全部排完,下周一(8月31日)填自评单</t>
@@ -5616,14 +5618,14 @@
     <col width="46" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
+    <row r="1" ht="64" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>四年级暑假 · 第8周 收尾冲刺(8月31日 周一)     9月1日开学!</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="26" customHeight="1">
+    <row r="2" ht="52" customHeight="1">
       <c r="A2" s="50" t="inlineStr">
         <is>
           <t>8月31日(周一)当日安排</t>
@@ -5637,7 +5639,7 @@
       </c>
       <c r="D2" s="53" t="n"/>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="68" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t>数学</t>
@@ -5655,7 +5657,7 @@
       </c>
       <c r="D3" s="54" t="n"/>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="68" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
           <t>数学</t>
@@ -5673,7 +5675,7 @@
       </c>
       <c r="D4" s="54" t="n"/>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="68" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
           <t>数学</t>
@@ -5691,7 +5693,7 @@
       </c>
       <c r="D5" s="54" t="n"/>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="68" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>英语</t>
@@ -5709,7 +5711,7 @@
       </c>
       <c r="D6" s="54" t="n"/>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="68" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
           <t>英语</t>
@@ -5727,7 +5729,7 @@
       </c>
       <c r="D7" s="54" t="n"/>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="68" customHeight="1">
       <c r="A8" s="18" t="inlineStr">
         <is>
           <t>体育</t>
@@ -5745,7 +5747,7 @@
       </c>
       <c r="D8" s="54" t="n"/>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="68" customHeight="1">
       <c r="A9" s="18" t="inlineStr">
         <is>
           <t>体育</t>
@@ -5763,7 +5765,7 @@
       </c>
       <c r="D9" s="54" t="n"/>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="68" customHeight="1">
       <c r="A10" s="55" t="inlineStr">
         <is>
           <t>整理</t>
@@ -5781,7 +5783,7 @@
       </c>
       <c r="D10" s="54" t="n"/>
     </row>
-    <row r="11" ht="28" customHeight="1">
+    <row r="11" ht="56" customHeight="1">
       <c r="A11" s="57" t="inlineStr">
         <is>
           <t>★ 8月29日(周六)、30日(周日)属于第7周页:综合练习卷第7、8份安排在这两天。如有未完成项目,利用这三天全部补齐!</t>

--- a/summer-homework/四年级暑假作业计划表.xlsx
+++ b/summer-homework/四年级暑假作业计划表.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,20 +54,21 @@
       <name val="微软雅黑"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="微软雅黑"/>
-      <sz val="10.5"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <b val="1"/>
-      <sz val="9.5"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <sz val="9.5"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="微软雅黑"/>
@@ -89,11 +90,16 @@
     </font>
     <font>
       <name val="微软雅黑"/>
-      <sz val="10"/>
+      <sz val="10.5"/>
     </font>
     <font>
       <name val="微软雅黑"/>
-      <sz val="9"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <sz val="10.5"/>
     </font>
     <font>
       <name val="微软雅黑"/>
@@ -105,7 +111,7 @@
       <name val="微软雅黑"/>
       <b val="1"/>
       <color rgb="007F6000"/>
-      <sz val="9.5"/>
+      <sz val="10.5"/>
     </font>
     <font>
       <name val="微软雅黑"/>
@@ -115,9 +121,7 @@
     </font>
     <font>
       <name val="微软雅黑"/>
-      <b val="1"/>
-      <color rgb="007F6000"/>
-      <sz val="10.5"/>
+      <sz val="11.5"/>
     </font>
   </fonts>
   <fills count="18">
@@ -267,13 +271,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -284,10 +288,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -298,10 +302,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -312,26 +316,35 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -342,79 +355,97 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1222,200 +1253,200 @@
           <t>周次</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B27" s="23" t="inlineStr">
         <is>
           <t>数学</t>
         </is>
       </c>
-      <c r="C27" s="12" t="inlineStr">
+      <c r="C27" s="24" t="inlineStr">
         <is>
           <t>英语</t>
         </is>
       </c>
-      <c r="D27" s="18" t="inlineStr">
+      <c r="D27" s="25" t="inlineStr">
         <is>
           <t>体育</t>
         </is>
       </c>
     </row>
     <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="23" t="inlineStr">
+      <c r="A28" s="26" t="inlineStr">
         <is>
           <t>第1周 7.13–7.19</t>
         </is>
       </c>
-      <c r="B28" s="24" t="inlineStr">
+      <c r="B28" s="27" t="inlineStr">
         <is>
           <t>口算计算(一~五)/ 试卷第1份(六)</t>
         </is>
       </c>
-      <c r="C28" s="24" t="inlineStr">
+      <c r="C28" s="27" t="inlineStr">
         <is>
           <t>朗读+抄写造句(一~四)/ 阅读3篇(一三五)</t>
         </is>
       </c>
-      <c r="D28" s="24" t="inlineStr">
+      <c r="D28" s="27" t="inlineStr">
         <is>
           <t>按课表锻炼+记成绩+家长签字</t>
         </is>
       </c>
     </row>
     <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="23" t="inlineStr">
+      <c r="A29" s="26" t="inlineStr">
         <is>
           <t>第2周 7.20–7.26</t>
         </is>
       </c>
-      <c r="B29" s="25" t="inlineStr">
+      <c r="B29" s="28" t="inlineStr">
         <is>
           <t>口算计算 / 试卷第2份(六)</t>
         </is>
       </c>
-      <c r="C29" s="25" t="inlineStr">
+      <c r="C29" s="28" t="inlineStr">
         <is>
           <t>同第1周</t>
         </is>
       </c>
-      <c r="D29" s="25" t="inlineStr">
+      <c r="D29" s="28" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
     </row>
     <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="23" t="inlineStr">
+      <c r="A30" s="26" t="inlineStr">
         <is>
           <t>第3周 7.27–8.2</t>
         </is>
       </c>
-      <c r="B30" s="24" t="inlineStr">
+      <c r="B30" s="27" t="inlineStr">
         <is>
           <t>口算计算 / 试卷第3份(六)</t>
         </is>
       </c>
-      <c r="C30" s="24" t="inlineStr">
+      <c r="C30" s="27" t="inlineStr">
         <is>
           <t>同第1周</t>
         </is>
       </c>
-      <c r="D30" s="24" t="inlineStr">
+      <c r="D30" s="27" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
     </row>
     <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="23" t="inlineStr">
+      <c r="A31" s="26" t="inlineStr">
         <is>
           <t>第4周 8.3–8.9</t>
         </is>
       </c>
-      <c r="B31" s="25" t="inlineStr">
+      <c r="B31" s="28" t="inlineStr">
         <is>
           <t>口算计算 / 试卷第4份(六)/ ★实践①每天记气温,周日绘统计图</t>
         </is>
       </c>
-      <c r="C31" s="25" t="inlineStr">
+      <c r="C31" s="28" t="inlineStr">
         <is>
           <t>同第1周</t>
         </is>
       </c>
-      <c r="D31" s="25" t="inlineStr">
+      <c r="D31" s="28" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
     </row>
     <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="23" t="inlineStr">
+      <c r="A32" s="26" t="inlineStr">
         <is>
           <t>第5周 8.10–8.16</t>
         </is>
       </c>
-      <c r="B32" s="24" t="inlineStr">
+      <c r="B32" s="27" t="inlineStr">
         <is>
           <t>口算计算 / 试卷第5份(六)</t>
         </is>
       </c>
-      <c r="C32" s="24" t="inlineStr">
+      <c r="C32" s="27" t="inlineStr">
         <is>
           <t>朗读+抄写(一~四)/ 阅读最后一周(一三五)/ ★选做英文歌(五)</t>
         </is>
       </c>
-      <c r="D32" s="24" t="inlineStr">
+      <c r="D32" s="27" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
     </row>
     <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="23" t="inlineStr">
+      <c r="A33" s="26" t="inlineStr">
         <is>
           <t>第6周 8.17–8.23</t>
         </is>
       </c>
-      <c r="B33" s="25" t="inlineStr">
+      <c r="B33" s="28" t="inlineStr">
         <is>
           <t>口算计算 / 试卷第6份(六)/ ★实践②周日设计密铺图案</t>
         </is>
       </c>
-      <c r="C33" s="25" t="inlineStr">
+      <c r="C33" s="28" t="inlineStr">
         <is>
           <t>朗读+抄写最后一周(一~四)/ ★英文歌(五)</t>
         </is>
       </c>
-      <c r="D33" s="25" t="inlineStr">
+      <c r="D33" s="28" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
     </row>
     <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="23" t="inlineStr">
+      <c r="A34" s="26" t="inlineStr">
         <is>
           <t>第7周 8.24–8.30</t>
         </is>
       </c>
-      <c r="B34" s="24" t="inlineStr">
+      <c r="B34" s="27" t="inlineStr">
         <is>
           <t>口算计算 / ★试卷第7份(六)、第8份(日)</t>
         </is>
       </c>
-      <c r="C34" s="24" t="inlineStr">
+      <c r="C34" s="27" t="inlineStr">
         <is>
           <t>★A3古诗海报(一~五)/ ★选做视听(三、五)</t>
         </is>
       </c>
-      <c r="D34" s="24" t="inlineStr">
+      <c r="D34" s="27" t="inlineStr">
         <is>
           <t>任务单最后一周,填“注明”最好成绩</t>
         </is>
       </c>
     </row>
     <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="23" t="inlineStr">
+      <c r="A35" s="26" t="inlineStr">
         <is>
           <t>第8周 8.31</t>
         </is>
       </c>
-      <c r="B35" s="25" t="inlineStr">
+      <c r="B35" s="28" t="inlineStr">
         <is>
           <t>清点8份试卷+2项实践作业</t>
         </is>
       </c>
-      <c r="C35" s="25" t="inlineStr">
+      <c r="C35" s="28" t="inlineStr">
         <is>
           <t>填写自评单(9月1日上交)</t>
         </is>
       </c>
-      <c r="D35" s="25" t="inlineStr">
+      <c r="D35" s="28" t="inlineStr">
         <is>
           <t>自由锻炼,补齐签字</t>
         </is>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="26" t="inlineStr">
+      <c r="A36" s="29" t="inlineStr">
         <is>
           <t>★ 使用方法:每周日晚打印下一周的“第N周”工作表(A4横向,已设置好一页打印),贴在书桌前;孩子每完成一项在□打✓,周日晚家长检查并签字。英语作业不含周六日及法定节假日(暑期内无法定节假日)。</t>
         </is>
@@ -1480,118 +1511,118 @@
   </cols>
   <sheetData>
     <row r="1" ht="58.2" customHeight="1">
-      <c r="A1" s="27" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>四年级暑假每日安排 · 第1周(7月13日—7月19日)    完成一项在□里打✓</t>
         </is>
       </c>
     </row>
     <row r="2" ht="58.2" customHeight="1">
-      <c r="A2" s="28" t="inlineStr">
+      <c r="A2" s="31" t="inlineStr">
         <is>
           <t>科目</t>
         </is>
       </c>
-      <c r="B2" s="28" t="inlineStr">
+      <c r="B2" s="31" t="inlineStr">
         <is>
           <t>任务内容</t>
         </is>
       </c>
-      <c r="C2" s="28" t="inlineStr">
+      <c r="C2" s="31" t="inlineStr">
         <is>
           <t>周一
 7月13日</t>
         </is>
       </c>
-      <c r="D2" s="28" t="inlineStr">
+      <c r="D2" s="31" t="inlineStr">
         <is>
           <t>周二
 7月14日</t>
         </is>
       </c>
-      <c r="E2" s="28" t="inlineStr">
+      <c r="E2" s="31" t="inlineStr">
         <is>
           <t>周三
 7月15日</t>
         </is>
       </c>
-      <c r="F2" s="28" t="inlineStr">
+      <c r="F2" s="31" t="inlineStr">
         <is>
           <t>周四
 7月16日</t>
         </is>
       </c>
-      <c r="G2" s="28" t="inlineStr">
+      <c r="G2" s="31" t="inlineStr">
         <is>
           <t>周五
 7月17日</t>
         </is>
       </c>
-      <c r="H2" s="29" t="inlineStr">
+      <c r="H2" s="32" t="inlineStr">
         <is>
           <t>周六
 7月18日</t>
         </is>
       </c>
-      <c r="I2" s="29" t="inlineStr">
+      <c r="I2" s="32" t="inlineStr">
         <is>
           <t>周日
 7月19日</t>
         </is>
       </c>
-      <c r="J2" s="28" t="inlineStr">
+      <c r="J2" s="31" t="inlineStr">
         <is>
           <t>要求 / 备注</t>
         </is>
       </c>
     </row>
     <row r="3" ht="46.6" customHeight="1">
-      <c r="A3" s="30" t="inlineStr">
+      <c r="A3" s="33" t="inlineStr">
         <is>
           <t>数学</t>
         </is>
       </c>
-      <c r="B3" s="31" t="inlineStr">
+      <c r="B3" s="34" t="inlineStr">
         <is>
           <t>口算 15~20 道(题目自备)</t>
         </is>
       </c>
-      <c r="C3" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="D3" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="E3" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="F3" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="G3" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="H3" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I3" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J3" s="34" t="inlineStr">
+      <c r="C3" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="D3" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="E3" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="F3" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="G3" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="H3" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I3" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J3" s="37" t="inlineStr">
         <is>
           <t>每日基础练习</t>
         </is>
@@ -1599,47 +1630,47 @@
     </row>
     <row r="4" ht="46.6" customHeight="1">
       <c r="A4" s="3" t="n"/>
-      <c r="B4" s="31" t="inlineStr">
+      <c r="B4" s="34" t="inlineStr">
         <is>
           <t>计算 4 道:三位数÷两位数 2道 + 小数乘法 2道</t>
         </is>
       </c>
-      <c r="C4" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="D4" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="E4" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="F4" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="G4" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="H4" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I4" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J4" s="34" t="inlineStr">
+      <c r="C4" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="D4" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="E4" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="F4" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="G4" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="H4" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I4" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J4" s="37" t="inlineStr">
         <is>
           <t>每日基础练习</t>
         </is>
@@ -1647,47 +1678,47 @@
     </row>
     <row r="5" ht="54.3" customHeight="1">
       <c r="A5" s="3" t="n"/>
-      <c r="B5" s="31" t="inlineStr">
+      <c r="B5" s="34" t="inlineStr">
         <is>
           <t>综合练习卷(每周1~2份,按8周计)</t>
         </is>
       </c>
-      <c r="C5" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D5" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E5" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H5" s="32" t="inlineStr">
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" s="35" t="inlineStr">
         <is>
           <t>□ 第1份(必做)</t>
         </is>
       </c>
-      <c r="I5" s="32" t="inlineStr">
+      <c r="I5" s="35" t="inlineStr">
         <is>
           <t>□ 加练1份(选做)</t>
         </is>
       </c>
-      <c r="J5" s="34" t="inlineStr">
+      <c r="J5" s="37" t="inlineStr">
         <is>
           <t>三选一:①数练活页卷 ②《5.3全优卷》剩余试卷 ③自备练习卷</t>
         </is>
@@ -1695,12 +1726,12 @@
     </row>
     <row r="6" ht="38.8" customHeight="1">
       <c r="A6" s="3" t="n"/>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>选做:《教材全解》拓展题 / 与家长商定提高内容</t>
         </is>
       </c>
-      <c r="C6" s="32" t="inlineStr">
+      <c r="C6" s="38" t="inlineStr">
         <is>
           <t>学有余力时安排,不做硬性打卡</t>
         </is>
@@ -1711,59 +1742,59 @@
       <c r="G6" s="5" t="n"/>
       <c r="H6" s="5" t="n"/>
       <c r="I6" s="5" t="n"/>
-      <c r="J6" s="34" t="inlineStr">
+      <c r="J6" s="37" t="inlineStr">
         <is>
           <t>自行安排</t>
         </is>
       </c>
     </row>
     <row r="7" ht="46.6" customHeight="1">
-      <c r="A7" s="35" t="inlineStr">
+      <c r="A7" s="39" t="inlineStr">
         <is>
           <t>英语</t>
         </is>
       </c>
-      <c r="B7" s="36" t="inlineStr">
+      <c r="B7" s="40" t="inlineStr">
         <is>
           <t>必做① 每天大声朗读三下课本(每次5分钟)</t>
         </is>
       </c>
-      <c r="C7" s="37" t="inlineStr">
+      <c r="C7" s="41" t="inlineStr">
         <is>
           <t>□ 5分钟</t>
         </is>
       </c>
-      <c r="D7" s="37" t="inlineStr">
+      <c r="D7" s="41" t="inlineStr">
         <is>
           <t>□ 5分钟</t>
         </is>
       </c>
-      <c r="E7" s="37" t="inlineStr">
+      <c r="E7" s="41" t="inlineStr">
         <is>
           <t>□ 5分钟</t>
         </is>
       </c>
-      <c r="F7" s="37" t="inlineStr">
+      <c r="F7" s="41" t="inlineStr">
         <is>
           <t>□ 5分钟</t>
         </is>
       </c>
-      <c r="G7" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H7" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I7" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J7" s="38" t="inlineStr">
+      <c r="G7" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I7" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J7" s="42" t="inlineStr">
         <is>
           <t>全假期共24次;第1~6周每周4次(本周为第1~4次)</t>
         </is>
@@ -1771,47 +1802,47 @@
     </row>
     <row r="8" ht="46.6" customHeight="1">
       <c r="A8" s="9" t="n"/>
-      <c r="B8" s="36" t="inlineStr">
+      <c r="B8" s="40" t="inlineStr">
         <is>
           <t>必做② 抄写四上&amp;四下单词/词组并造句(每次10分钟)</t>
         </is>
       </c>
-      <c r="C8" s="37" t="inlineStr">
+      <c r="C8" s="41" t="inlineStr">
         <is>
           <t>□ 10分钟</t>
         </is>
       </c>
-      <c r="D8" s="37" t="inlineStr">
+      <c r="D8" s="41" t="inlineStr">
         <is>
           <t>□ 10分钟</t>
         </is>
       </c>
-      <c r="E8" s="37" t="inlineStr">
+      <c r="E8" s="41" t="inlineStr">
         <is>
           <t>□ 10分钟</t>
         </is>
       </c>
-      <c r="F8" s="37" t="inlineStr">
+      <c r="F8" s="41" t="inlineStr">
         <is>
           <t>□ 10分钟</t>
         </is>
       </c>
-      <c r="G8" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H8" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I8" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J8" s="38" t="inlineStr">
+      <c r="G8" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J8" s="42" t="inlineStr">
         <is>
           <t>全假期共24次;第1~6周每周4次</t>
         </is>
@@ -1819,64 +1850,64 @@
     </row>
     <row r="9" ht="46.6" customHeight="1">
       <c r="A9" s="9" t="n"/>
-      <c r="B9" s="36" t="inlineStr">
+      <c r="B9" s="40" t="inlineStr">
         <is>
           <t>必做③ 完成英语阅读题3篇(每次15分钟)</t>
         </is>
       </c>
-      <c r="C9" s="37" t="inlineStr">
+      <c r="C9" s="41" t="inlineStr">
         <is>
           <t>□ 3篇</t>
         </is>
       </c>
-      <c r="D9" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E9" s="37" t="inlineStr">
+      <c r="D9" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="41" t="inlineStr">
         <is>
           <t>□ 3篇</t>
         </is>
       </c>
-      <c r="F9" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G9" s="37" t="inlineStr">
+      <c r="F9" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="41" t="inlineStr">
         <is>
           <t>□ 3篇</t>
         </is>
       </c>
-      <c r="H9" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I9" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J9" s="38" t="inlineStr">
+      <c r="H9" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I9" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J9" s="42" t="inlineStr">
         <is>
           <t>全假期共15次;第1~5周每周一、三、五</t>
         </is>
       </c>
     </row>
     <row r="10" ht="186.3" customHeight="1">
-      <c r="A10" s="39" t="inlineStr">
+      <c r="A10" s="43" t="inlineStr">
         <is>
           <t>体育</t>
         </is>
       </c>
-      <c r="B10" s="40" t="inlineStr">
+      <c r="B10" s="44" t="inlineStr">
         <is>
           <t>每日锻炼(先热身 → 练习 → 放松拉伸)</t>
         </is>
       </c>
-      <c r="C10" s="41" t="inlineStr">
+      <c r="C10" s="44" t="inlineStr">
         <is>
           <t>□ 热身
 □ 1分钟计时跳绳×4组
@@ -1884,7 +1915,7 @@
 □ 坐位体前屈拉伸1分钟</t>
         </is>
       </c>
-      <c r="D10" s="41" t="inlineStr">
+      <c r="D10" s="44" t="inlineStr">
         <is>
           <t>□ 热身
 □ 跳绳200个/组×4组
@@ -1893,7 +1924,7 @@
 □ 坐位体前屈1分钟</t>
         </is>
       </c>
-      <c r="E10" s="41" t="inlineStr">
+      <c r="E10" s="44" t="inlineStr">
         <is>
           <t>□ 热身
 □ 1分钟计时跳绳×4组
@@ -1902,7 +1933,7 @@
 □ 放松拉伸</t>
         </is>
       </c>
-      <c r="F10" s="41" t="inlineStr">
+      <c r="F10" s="44" t="inlineStr">
         <is>
           <t>□ 热身
 □ 3分钟耐力跳绳
@@ -1910,7 +1941,7 @@
 □ 放松拉伸</t>
         </is>
       </c>
-      <c r="G10" s="41" t="inlineStr">
+      <c r="G10" s="44" t="inlineStr">
         <is>
           <t>□ 热身
 □ 耐力跑2公里
@@ -1919,17 +1950,17 @@
 □ 放松拉伸</t>
         </is>
       </c>
-      <c r="H10" s="33" t="inlineStr">
+      <c r="H10" s="45" t="inlineStr">
         <is>
           <t>休息 · 自由活动</t>
         </is>
       </c>
-      <c r="I10" s="33" t="inlineStr">
+      <c r="I10" s="45" t="inlineStr">
         <is>
           <t>休息 · 自由活动</t>
         </is>
       </c>
-      <c r="J10" s="42" t="inlineStr">
+      <c r="J10" s="46" t="inlineStr">
         <is>
           <t>目标:跳绳200个/分钟;仰卧起坐49个/分钟;体前屈膝盖伸直、手指过脚尖;有条件可加练加速跑</t>
         </is>
@@ -1937,47 +1968,47 @@
     </row>
     <row r="11" ht="50.4" customHeight="1">
       <c r="A11" s="15" t="n"/>
-      <c r="B11" s="40" t="inlineStr">
+      <c r="B11" s="44" t="inlineStr">
         <is>
           <t>成绩记录(把当天成绩写进括号)</t>
         </is>
       </c>
-      <c r="C11" s="41" t="inlineStr">
+      <c r="C11" s="47" t="inlineStr">
         <is>
           <t>(        )</t>
         </is>
       </c>
-      <c r="D11" s="41" t="inlineStr">
+      <c r="D11" s="47" t="inlineStr">
         <is>
           <t>(        )</t>
         </is>
       </c>
-      <c r="E11" s="41" t="inlineStr">
+      <c r="E11" s="47" t="inlineStr">
         <is>
           <t>(        )</t>
         </is>
       </c>
-      <c r="F11" s="41" t="inlineStr">
+      <c r="F11" s="47" t="inlineStr">
         <is>
           <t>(        )</t>
         </is>
       </c>
-      <c r="G11" s="41" t="inlineStr">
+      <c r="G11" s="47" t="inlineStr">
         <is>
           <t>(        )</t>
         </is>
       </c>
-      <c r="H11" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I11" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J11" s="42" t="inlineStr">
+      <c r="H11" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I11" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J11" s="46" t="inlineStr">
         <is>
           <t>开学交任务单,学校按完成情况评优体奖章</t>
         </is>
@@ -1985,39 +2016,39 @@
     </row>
     <row r="12" ht="50.4" customHeight="1">
       <c r="A12" s="15" t="n"/>
-      <c r="B12" s="43" t="inlineStr">
+      <c r="B12" s="48" t="inlineStr">
         <is>
           <t>家长点评签字(每周一次)</t>
         </is>
       </c>
-      <c r="C12" s="44" t="inlineStr"/>
-      <c r="D12" s="44" t="n"/>
-      <c r="E12" s="44" t="n"/>
-      <c r="F12" s="44" t="n"/>
-      <c r="G12" s="44" t="n"/>
-      <c r="H12" s="44" t="n"/>
-      <c r="I12" s="44" t="n"/>
-      <c r="J12" s="42" t="inlineStr">
+      <c r="C12" s="49" t="inlineStr"/>
+      <c r="D12" s="49" t="n"/>
+      <c r="E12" s="49" t="n"/>
+      <c r="F12" s="49" t="n"/>
+      <c r="G12" s="49" t="n"/>
+      <c r="H12" s="49" t="n"/>
+      <c r="I12" s="49" t="n"/>
+      <c r="J12" s="46" t="inlineStr">
         <is>
           <t>对应任务单“家长点评签字”栏</t>
         </is>
       </c>
     </row>
     <row r="13" ht="50.4" customHeight="1">
-      <c r="A13" s="45" t="inlineStr">
+      <c r="A13" s="50" t="inlineStr">
         <is>
           <t>★ 英语作业不含周六日和法定节假日 · 体育锻炼注意防暑降温 · 数学实践作业4选2(本表建议做③气温统计、④密铺图案,也可换成①数学游戏、②小区调查)</t>
         </is>
       </c>
-      <c r="B13" s="46" t="n"/>
-      <c r="C13" s="46" t="n"/>
-      <c r="D13" s="46" t="n"/>
-      <c r="E13" s="46" t="n"/>
-      <c r="F13" s="46" t="n"/>
-      <c r="G13" s="46" t="n"/>
-      <c r="H13" s="46" t="n"/>
-      <c r="I13" s="46" t="n"/>
-      <c r="J13" s="46" t="n"/>
+      <c r="B13" s="51" t="n"/>
+      <c r="C13" s="51" t="n"/>
+      <c r="D13" s="51" t="n"/>
+      <c r="E13" s="51" t="n"/>
+      <c r="F13" s="51" t="n"/>
+      <c r="G13" s="51" t="n"/>
+      <c r="H13" s="51" t="n"/>
+      <c r="I13" s="51" t="n"/>
+      <c r="J13" s="51" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -2058,118 +2089,118 @@
   </cols>
   <sheetData>
     <row r="1" ht="58.2" customHeight="1">
-      <c r="A1" s="27" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>四年级暑假每日安排 · 第2周(7月20日—7月26日)    完成一项在□里打✓</t>
         </is>
       </c>
     </row>
     <row r="2" ht="58.2" customHeight="1">
-      <c r="A2" s="28" t="inlineStr">
+      <c r="A2" s="31" t="inlineStr">
         <is>
           <t>科目</t>
         </is>
       </c>
-      <c r="B2" s="28" t="inlineStr">
+      <c r="B2" s="31" t="inlineStr">
         <is>
           <t>任务内容</t>
         </is>
       </c>
-      <c r="C2" s="28" t="inlineStr">
+      <c r="C2" s="31" t="inlineStr">
         <is>
           <t>周一
 7月20日</t>
         </is>
       </c>
-      <c r="D2" s="28" t="inlineStr">
+      <c r="D2" s="31" t="inlineStr">
         <is>
           <t>周二
 7月21日</t>
         </is>
       </c>
-      <c r="E2" s="28" t="inlineStr">
+      <c r="E2" s="31" t="inlineStr">
         <is>
           <t>周三
 7月22日</t>
         </is>
       </c>
-      <c r="F2" s="28" t="inlineStr">
+      <c r="F2" s="31" t="inlineStr">
         <is>
           <t>周四
 7月23日</t>
         </is>
       </c>
-      <c r="G2" s="28" t="inlineStr">
+      <c r="G2" s="31" t="inlineStr">
         <is>
           <t>周五
 7月24日</t>
         </is>
       </c>
-      <c r="H2" s="29" t="inlineStr">
+      <c r="H2" s="32" t="inlineStr">
         <is>
           <t>周六
 7月25日</t>
         </is>
       </c>
-      <c r="I2" s="29" t="inlineStr">
+      <c r="I2" s="32" t="inlineStr">
         <is>
           <t>周日
 7月26日</t>
         </is>
       </c>
-      <c r="J2" s="28" t="inlineStr">
+      <c r="J2" s="31" t="inlineStr">
         <is>
           <t>要求 / 备注</t>
         </is>
       </c>
     </row>
     <row r="3" ht="46.6" customHeight="1">
-      <c r="A3" s="30" t="inlineStr">
+      <c r="A3" s="33" t="inlineStr">
         <is>
           <t>数学</t>
         </is>
       </c>
-      <c r="B3" s="31" t="inlineStr">
+      <c r="B3" s="34" t="inlineStr">
         <is>
           <t>口算 15~20 道(题目自备)</t>
         </is>
       </c>
-      <c r="C3" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="D3" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="E3" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="F3" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="G3" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="H3" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I3" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J3" s="34" t="inlineStr">
+      <c r="C3" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="D3" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="E3" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="F3" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="G3" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="H3" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I3" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J3" s="37" t="inlineStr">
         <is>
           <t>每日基础练习</t>
         </is>
@@ -2177,47 +2208,47 @@
     </row>
     <row r="4" ht="46.6" customHeight="1">
       <c r="A4" s="3" t="n"/>
-      <c r="B4" s="31" t="inlineStr">
+      <c r="B4" s="34" t="inlineStr">
         <is>
           <t>计算 4 道:三位数÷两位数 2道 + 小数乘法 2道</t>
         </is>
       </c>
-      <c r="C4" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="D4" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="E4" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="F4" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="G4" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="H4" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I4" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J4" s="34" t="inlineStr">
+      <c r="C4" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="D4" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="E4" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="F4" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="G4" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="H4" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I4" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J4" s="37" t="inlineStr">
         <is>
           <t>每日基础练习</t>
         </is>
@@ -2225,47 +2256,47 @@
     </row>
     <row r="5" ht="54.3" customHeight="1">
       <c r="A5" s="3" t="n"/>
-      <c r="B5" s="31" t="inlineStr">
+      <c r="B5" s="34" t="inlineStr">
         <is>
           <t>综合练习卷(每周1~2份,按8周计)</t>
         </is>
       </c>
-      <c r="C5" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D5" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E5" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H5" s="32" t="inlineStr">
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" s="35" t="inlineStr">
         <is>
           <t>□ 第2份(必做)</t>
         </is>
       </c>
-      <c r="I5" s="32" t="inlineStr">
+      <c r="I5" s="35" t="inlineStr">
         <is>
           <t>□ 加练1份(选做)</t>
         </is>
       </c>
-      <c r="J5" s="34" t="inlineStr">
+      <c r="J5" s="37" t="inlineStr">
         <is>
           <t>三选一:①数练活页卷 ②《5.3全优卷》剩余试卷 ③自备练习卷</t>
         </is>
@@ -2273,12 +2304,12 @@
     </row>
     <row r="6" ht="38.8" customHeight="1">
       <c r="A6" s="3" t="n"/>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>选做:《教材全解》拓展题 / 与家长商定提高内容</t>
         </is>
       </c>
-      <c r="C6" s="32" t="inlineStr">
+      <c r="C6" s="38" t="inlineStr">
         <is>
           <t>学有余力时安排,不做硬性打卡</t>
         </is>
@@ -2289,59 +2320,59 @@
       <c r="G6" s="5" t="n"/>
       <c r="H6" s="5" t="n"/>
       <c r="I6" s="5" t="n"/>
-      <c r="J6" s="34" t="inlineStr">
+      <c r="J6" s="37" t="inlineStr">
         <is>
           <t>自行安排</t>
         </is>
       </c>
     </row>
     <row r="7" ht="46.6" customHeight="1">
-      <c r="A7" s="35" t="inlineStr">
+      <c r="A7" s="39" t="inlineStr">
         <is>
           <t>英语</t>
         </is>
       </c>
-      <c r="B7" s="36" t="inlineStr">
+      <c r="B7" s="40" t="inlineStr">
         <is>
           <t>必做① 每天大声朗读三下课本(每次5分钟)</t>
         </is>
       </c>
-      <c r="C7" s="37" t="inlineStr">
+      <c r="C7" s="41" t="inlineStr">
         <is>
           <t>□ 5分钟</t>
         </is>
       </c>
-      <c r="D7" s="37" t="inlineStr">
+      <c r="D7" s="41" t="inlineStr">
         <is>
           <t>□ 5分钟</t>
         </is>
       </c>
-      <c r="E7" s="37" t="inlineStr">
+      <c r="E7" s="41" t="inlineStr">
         <is>
           <t>□ 5分钟</t>
         </is>
       </c>
-      <c r="F7" s="37" t="inlineStr">
+      <c r="F7" s="41" t="inlineStr">
         <is>
           <t>□ 5分钟</t>
         </is>
       </c>
-      <c r="G7" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H7" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I7" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J7" s="38" t="inlineStr">
+      <c r="G7" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I7" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J7" s="42" t="inlineStr">
         <is>
           <t>全假期共24次;第1~6周每周4次(本周为第5~8次)</t>
         </is>
@@ -2349,47 +2380,47 @@
     </row>
     <row r="8" ht="46.6" customHeight="1">
       <c r="A8" s="9" t="n"/>
-      <c r="B8" s="36" t="inlineStr">
+      <c r="B8" s="40" t="inlineStr">
         <is>
           <t>必做② 抄写四上&amp;四下单词/词组并造句(每次10分钟)</t>
         </is>
       </c>
-      <c r="C8" s="37" t="inlineStr">
+      <c r="C8" s="41" t="inlineStr">
         <is>
           <t>□ 10分钟</t>
         </is>
       </c>
-      <c r="D8" s="37" t="inlineStr">
+      <c r="D8" s="41" t="inlineStr">
         <is>
           <t>□ 10分钟</t>
         </is>
       </c>
-      <c r="E8" s="37" t="inlineStr">
+      <c r="E8" s="41" t="inlineStr">
         <is>
           <t>□ 10分钟</t>
         </is>
       </c>
-      <c r="F8" s="37" t="inlineStr">
+      <c r="F8" s="41" t="inlineStr">
         <is>
           <t>□ 10分钟</t>
         </is>
       </c>
-      <c r="G8" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H8" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I8" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J8" s="38" t="inlineStr">
+      <c r="G8" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J8" s="42" t="inlineStr">
         <is>
           <t>全假期共24次;第1~6周每周4次</t>
         </is>
@@ -2397,64 +2428,64 @@
     </row>
     <row r="9" ht="46.6" customHeight="1">
       <c r="A9" s="9" t="n"/>
-      <c r="B9" s="36" t="inlineStr">
+      <c r="B9" s="40" t="inlineStr">
         <is>
           <t>必做③ 完成英语阅读题3篇(每次15分钟)</t>
         </is>
       </c>
-      <c r="C9" s="37" t="inlineStr">
+      <c r="C9" s="41" t="inlineStr">
         <is>
           <t>□ 3篇</t>
         </is>
       </c>
-      <c r="D9" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E9" s="37" t="inlineStr">
+      <c r="D9" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="41" t="inlineStr">
         <is>
           <t>□ 3篇</t>
         </is>
       </c>
-      <c r="F9" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G9" s="37" t="inlineStr">
+      <c r="F9" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="41" t="inlineStr">
         <is>
           <t>□ 3篇</t>
         </is>
       </c>
-      <c r="H9" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I9" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J9" s="38" t="inlineStr">
+      <c r="H9" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I9" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J9" s="42" t="inlineStr">
         <is>
           <t>全假期共15次;第1~5周每周一、三、五</t>
         </is>
       </c>
     </row>
     <row r="10" ht="186.3" customHeight="1">
-      <c r="A10" s="39" t="inlineStr">
+      <c r="A10" s="43" t="inlineStr">
         <is>
           <t>体育</t>
         </is>
       </c>
-      <c r="B10" s="40" t="inlineStr">
+      <c r="B10" s="44" t="inlineStr">
         <is>
           <t>每日锻炼(先热身 → 练习 → 放松拉伸)</t>
         </is>
       </c>
-      <c r="C10" s="41" t="inlineStr">
+      <c r="C10" s="44" t="inlineStr">
         <is>
           <t>□ 热身
 □ 1分钟计时跳绳×4组
@@ -2462,7 +2493,7 @@
 □ 坐位体前屈拉伸1分钟</t>
         </is>
       </c>
-      <c r="D10" s="41" t="inlineStr">
+      <c r="D10" s="44" t="inlineStr">
         <is>
           <t>□ 热身
 □ 跳绳200个/组×4组
@@ -2471,7 +2502,7 @@
 □ 坐位体前屈1分钟</t>
         </is>
       </c>
-      <c r="E10" s="41" t="inlineStr">
+      <c r="E10" s="44" t="inlineStr">
         <is>
           <t>□ 热身
 □ 1分钟计时跳绳×4组
@@ -2480,7 +2511,7 @@
 □ 放松拉伸</t>
         </is>
       </c>
-      <c r="F10" s="41" t="inlineStr">
+      <c r="F10" s="44" t="inlineStr">
         <is>
           <t>□ 热身
 □ 3分钟耐力跳绳
@@ -2488,7 +2519,7 @@
 □ 放松拉伸</t>
         </is>
       </c>
-      <c r="G10" s="41" t="inlineStr">
+      <c r="G10" s="44" t="inlineStr">
         <is>
           <t>□ 热身
 □ 耐力跑2公里
@@ -2497,17 +2528,17 @@
 □ 放松拉伸</t>
         </is>
       </c>
-      <c r="H10" s="33" t="inlineStr">
+      <c r="H10" s="45" t="inlineStr">
         <is>
           <t>休息 · 自由活动</t>
         </is>
       </c>
-      <c r="I10" s="33" t="inlineStr">
+      <c r="I10" s="45" t="inlineStr">
         <is>
           <t>休息 · 自由活动</t>
         </is>
       </c>
-      <c r="J10" s="42" t="inlineStr">
+      <c r="J10" s="46" t="inlineStr">
         <is>
           <t>目标:跳绳200个/分钟;仰卧起坐49个/分钟;体前屈膝盖伸直、手指过脚尖;有条件可加练加速跑</t>
         </is>
@@ -2515,47 +2546,47 @@
     </row>
     <row r="11" ht="50.4" customHeight="1">
       <c r="A11" s="15" t="n"/>
-      <c r="B11" s="40" t="inlineStr">
+      <c r="B11" s="44" t="inlineStr">
         <is>
           <t>成绩记录(把当天成绩写进括号)</t>
         </is>
       </c>
-      <c r="C11" s="41" t="inlineStr">
+      <c r="C11" s="47" t="inlineStr">
         <is>
           <t>(        )</t>
         </is>
       </c>
-      <c r="D11" s="41" t="inlineStr">
+      <c r="D11" s="47" t="inlineStr">
         <is>
           <t>(        )</t>
         </is>
       </c>
-      <c r="E11" s="41" t="inlineStr">
+      <c r="E11" s="47" t="inlineStr">
         <is>
           <t>(        )</t>
         </is>
       </c>
-      <c r="F11" s="41" t="inlineStr">
+      <c r="F11" s="47" t="inlineStr">
         <is>
           <t>(        )</t>
         </is>
       </c>
-      <c r="G11" s="41" t="inlineStr">
+      <c r="G11" s="47" t="inlineStr">
         <is>
           <t>(        )</t>
         </is>
       </c>
-      <c r="H11" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I11" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J11" s="42" t="inlineStr">
+      <c r="H11" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I11" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J11" s="46" t="inlineStr">
         <is>
           <t>开学交任务单,学校按完成情况评优体奖章</t>
         </is>
@@ -2563,39 +2594,39 @@
     </row>
     <row r="12" ht="50.4" customHeight="1">
       <c r="A12" s="15" t="n"/>
-      <c r="B12" s="43" t="inlineStr">
+      <c r="B12" s="48" t="inlineStr">
         <is>
           <t>家长点评签字(每周一次)</t>
         </is>
       </c>
-      <c r="C12" s="44" t="inlineStr"/>
-      <c r="D12" s="44" t="n"/>
-      <c r="E12" s="44" t="n"/>
-      <c r="F12" s="44" t="n"/>
-      <c r="G12" s="44" t="n"/>
-      <c r="H12" s="44" t="n"/>
-      <c r="I12" s="44" t="n"/>
-      <c r="J12" s="42" t="inlineStr">
+      <c r="C12" s="49" t="inlineStr"/>
+      <c r="D12" s="49" t="n"/>
+      <c r="E12" s="49" t="n"/>
+      <c r="F12" s="49" t="n"/>
+      <c r="G12" s="49" t="n"/>
+      <c r="H12" s="49" t="n"/>
+      <c r="I12" s="49" t="n"/>
+      <c r="J12" s="46" t="inlineStr">
         <is>
           <t>对应任务单“家长点评签字”栏</t>
         </is>
       </c>
     </row>
     <row r="13" ht="50.4" customHeight="1">
-      <c r="A13" s="45" t="inlineStr">
+      <c r="A13" s="50" t="inlineStr">
         <is>
           <t>★ 英语作业不含周六日和法定节假日 · 体育锻炼注意防暑降温 · 数学实践作业4选2(本表建议做③气温统计、④密铺图案,也可换成①数学游戏、②小区调查)</t>
         </is>
       </c>
-      <c r="B13" s="46" t="n"/>
-      <c r="C13" s="46" t="n"/>
-      <c r="D13" s="46" t="n"/>
-      <c r="E13" s="46" t="n"/>
-      <c r="F13" s="46" t="n"/>
-      <c r="G13" s="46" t="n"/>
-      <c r="H13" s="46" t="n"/>
-      <c r="I13" s="46" t="n"/>
-      <c r="J13" s="46" t="n"/>
+      <c r="B13" s="51" t="n"/>
+      <c r="C13" s="51" t="n"/>
+      <c r="D13" s="51" t="n"/>
+      <c r="E13" s="51" t="n"/>
+      <c r="F13" s="51" t="n"/>
+      <c r="G13" s="51" t="n"/>
+      <c r="H13" s="51" t="n"/>
+      <c r="I13" s="51" t="n"/>
+      <c r="J13" s="51" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -2636,118 +2667,118 @@
   </cols>
   <sheetData>
     <row r="1" ht="58.2" customHeight="1">
-      <c r="A1" s="27" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>四年级暑假每日安排 · 第3周(7月27日—8月2日)    完成一项在□里打✓</t>
         </is>
       </c>
     </row>
     <row r="2" ht="58.2" customHeight="1">
-      <c r="A2" s="28" t="inlineStr">
+      <c r="A2" s="31" t="inlineStr">
         <is>
           <t>科目</t>
         </is>
       </c>
-      <c r="B2" s="28" t="inlineStr">
+      <c r="B2" s="31" t="inlineStr">
         <is>
           <t>任务内容</t>
         </is>
       </c>
-      <c r="C2" s="28" t="inlineStr">
+      <c r="C2" s="31" t="inlineStr">
         <is>
           <t>周一
 7月27日</t>
         </is>
       </c>
-      <c r="D2" s="28" t="inlineStr">
+      <c r="D2" s="31" t="inlineStr">
         <is>
           <t>周二
 7月28日</t>
         </is>
       </c>
-      <c r="E2" s="28" t="inlineStr">
+      <c r="E2" s="31" t="inlineStr">
         <is>
           <t>周三
 7月29日</t>
         </is>
       </c>
-      <c r="F2" s="28" t="inlineStr">
+      <c r="F2" s="31" t="inlineStr">
         <is>
           <t>周四
 7月30日</t>
         </is>
       </c>
-      <c r="G2" s="28" t="inlineStr">
+      <c r="G2" s="31" t="inlineStr">
         <is>
           <t>周五
 7月31日</t>
         </is>
       </c>
-      <c r="H2" s="29" t="inlineStr">
+      <c r="H2" s="32" t="inlineStr">
         <is>
           <t>周六
 8月1日</t>
         </is>
       </c>
-      <c r="I2" s="29" t="inlineStr">
+      <c r="I2" s="32" t="inlineStr">
         <is>
           <t>周日
 8月2日</t>
         </is>
       </c>
-      <c r="J2" s="28" t="inlineStr">
+      <c r="J2" s="31" t="inlineStr">
         <is>
           <t>要求 / 备注</t>
         </is>
       </c>
     </row>
     <row r="3" ht="46.6" customHeight="1">
-      <c r="A3" s="30" t="inlineStr">
+      <c r="A3" s="33" t="inlineStr">
         <is>
           <t>数学</t>
         </is>
       </c>
-      <c r="B3" s="31" t="inlineStr">
+      <c r="B3" s="34" t="inlineStr">
         <is>
           <t>口算 15~20 道(题目自备)</t>
         </is>
       </c>
-      <c r="C3" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="D3" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="E3" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="F3" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="G3" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="H3" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I3" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J3" s="34" t="inlineStr">
+      <c r="C3" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="D3" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="E3" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="F3" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="G3" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="H3" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I3" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J3" s="37" t="inlineStr">
         <is>
           <t>每日基础练习</t>
         </is>
@@ -2755,47 +2786,47 @@
     </row>
     <row r="4" ht="46.6" customHeight="1">
       <c r="A4" s="3" t="n"/>
-      <c r="B4" s="31" t="inlineStr">
+      <c r="B4" s="34" t="inlineStr">
         <is>
           <t>计算 4 道:三位数÷两位数 2道 + 小数乘法 2道</t>
         </is>
       </c>
-      <c r="C4" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="D4" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="E4" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="F4" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="G4" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="H4" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I4" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J4" s="34" t="inlineStr">
+      <c r="C4" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="D4" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="E4" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="F4" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="G4" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="H4" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I4" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J4" s="37" t="inlineStr">
         <is>
           <t>每日基础练习</t>
         </is>
@@ -2803,47 +2834,47 @@
     </row>
     <row r="5" ht="54.3" customHeight="1">
       <c r="A5" s="3" t="n"/>
-      <c r="B5" s="31" t="inlineStr">
+      <c r="B5" s="34" t="inlineStr">
         <is>
           <t>综合练习卷(每周1~2份,按8周计)</t>
         </is>
       </c>
-      <c r="C5" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D5" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E5" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H5" s="32" t="inlineStr">
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" s="35" t="inlineStr">
         <is>
           <t>□ 第3份(必做)</t>
         </is>
       </c>
-      <c r="I5" s="32" t="inlineStr">
+      <c r="I5" s="35" t="inlineStr">
         <is>
           <t>□ 加练1份(选做)</t>
         </is>
       </c>
-      <c r="J5" s="34" t="inlineStr">
+      <c r="J5" s="37" t="inlineStr">
         <is>
           <t>三选一:①数练活页卷 ②《5.3全优卷》剩余试卷 ③自备练习卷</t>
         </is>
@@ -2851,12 +2882,12 @@
     </row>
     <row r="6" ht="38.8" customHeight="1">
       <c r="A6" s="3" t="n"/>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>选做:《教材全解》拓展题 / 与家长商定提高内容</t>
         </is>
       </c>
-      <c r="C6" s="32" t="inlineStr">
+      <c r="C6" s="38" t="inlineStr">
         <is>
           <t>学有余力时安排,不做硬性打卡</t>
         </is>
@@ -2867,59 +2898,59 @@
       <c r="G6" s="5" t="n"/>
       <c r="H6" s="5" t="n"/>
       <c r="I6" s="5" t="n"/>
-      <c r="J6" s="34" t="inlineStr">
+      <c r="J6" s="37" t="inlineStr">
         <is>
           <t>自行安排</t>
         </is>
       </c>
     </row>
     <row r="7" ht="46.6" customHeight="1">
-      <c r="A7" s="35" t="inlineStr">
+      <c r="A7" s="39" t="inlineStr">
         <is>
           <t>英语</t>
         </is>
       </c>
-      <c r="B7" s="36" t="inlineStr">
+      <c r="B7" s="40" t="inlineStr">
         <is>
           <t>必做① 每天大声朗读三下课本(每次5分钟)</t>
         </is>
       </c>
-      <c r="C7" s="37" t="inlineStr">
+      <c r="C7" s="41" t="inlineStr">
         <is>
           <t>□ 5分钟</t>
         </is>
       </c>
-      <c r="D7" s="37" t="inlineStr">
+      <c r="D7" s="41" t="inlineStr">
         <is>
           <t>□ 5分钟</t>
         </is>
       </c>
-      <c r="E7" s="37" t="inlineStr">
+      <c r="E7" s="41" t="inlineStr">
         <is>
           <t>□ 5分钟</t>
         </is>
       </c>
-      <c r="F7" s="37" t="inlineStr">
+      <c r="F7" s="41" t="inlineStr">
         <is>
           <t>□ 5分钟</t>
         </is>
       </c>
-      <c r="G7" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H7" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I7" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J7" s="38" t="inlineStr">
+      <c r="G7" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I7" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J7" s="42" t="inlineStr">
         <is>
           <t>全假期共24次;第1~6周每周4次(本周为第9~12次)</t>
         </is>
@@ -2927,47 +2958,47 @@
     </row>
     <row r="8" ht="46.6" customHeight="1">
       <c r="A8" s="9" t="n"/>
-      <c r="B8" s="36" t="inlineStr">
+      <c r="B8" s="40" t="inlineStr">
         <is>
           <t>必做② 抄写四上&amp;四下单词/词组并造句(每次10分钟)</t>
         </is>
       </c>
-      <c r="C8" s="37" t="inlineStr">
+      <c r="C8" s="41" t="inlineStr">
         <is>
           <t>□ 10分钟</t>
         </is>
       </c>
-      <c r="D8" s="37" t="inlineStr">
+      <c r="D8" s="41" t="inlineStr">
         <is>
           <t>□ 10分钟</t>
         </is>
       </c>
-      <c r="E8" s="37" t="inlineStr">
+      <c r="E8" s="41" t="inlineStr">
         <is>
           <t>□ 10分钟</t>
         </is>
       </c>
-      <c r="F8" s="37" t="inlineStr">
+      <c r="F8" s="41" t="inlineStr">
         <is>
           <t>□ 10分钟</t>
         </is>
       </c>
-      <c r="G8" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H8" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I8" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J8" s="38" t="inlineStr">
+      <c r="G8" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J8" s="42" t="inlineStr">
         <is>
           <t>全假期共24次;第1~6周每周4次</t>
         </is>
@@ -2975,64 +3006,64 @@
     </row>
     <row r="9" ht="46.6" customHeight="1">
       <c r="A9" s="9" t="n"/>
-      <c r="B9" s="36" t="inlineStr">
+      <c r="B9" s="40" t="inlineStr">
         <is>
           <t>必做③ 完成英语阅读题3篇(每次15分钟)</t>
         </is>
       </c>
-      <c r="C9" s="37" t="inlineStr">
+      <c r="C9" s="41" t="inlineStr">
         <is>
           <t>□ 3篇</t>
         </is>
       </c>
-      <c r="D9" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E9" s="37" t="inlineStr">
+      <c r="D9" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="41" t="inlineStr">
         <is>
           <t>□ 3篇</t>
         </is>
       </c>
-      <c r="F9" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G9" s="37" t="inlineStr">
+      <c r="F9" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="41" t="inlineStr">
         <is>
           <t>□ 3篇</t>
         </is>
       </c>
-      <c r="H9" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I9" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J9" s="38" t="inlineStr">
+      <c r="H9" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I9" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J9" s="42" t="inlineStr">
         <is>
           <t>全假期共15次;第1~5周每周一、三、五</t>
         </is>
       </c>
     </row>
     <row r="10" ht="186.3" customHeight="1">
-      <c r="A10" s="39" t="inlineStr">
+      <c r="A10" s="43" t="inlineStr">
         <is>
           <t>体育</t>
         </is>
       </c>
-      <c r="B10" s="40" t="inlineStr">
+      <c r="B10" s="44" t="inlineStr">
         <is>
           <t>每日锻炼(先热身 → 练习 → 放松拉伸)</t>
         </is>
       </c>
-      <c r="C10" s="41" t="inlineStr">
+      <c r="C10" s="44" t="inlineStr">
         <is>
           <t>□ 热身
 □ 1分钟计时跳绳×4组
@@ -3040,7 +3071,7 @@
 □ 坐位体前屈拉伸1分钟</t>
         </is>
       </c>
-      <c r="D10" s="41" t="inlineStr">
+      <c r="D10" s="44" t="inlineStr">
         <is>
           <t>□ 热身
 □ 跳绳200个/组×4组
@@ -3049,7 +3080,7 @@
 □ 坐位体前屈1分钟</t>
         </is>
       </c>
-      <c r="E10" s="41" t="inlineStr">
+      <c r="E10" s="44" t="inlineStr">
         <is>
           <t>□ 热身
 □ 1分钟计时跳绳×4组
@@ -3058,7 +3089,7 @@
 □ 放松拉伸</t>
         </is>
       </c>
-      <c r="F10" s="41" t="inlineStr">
+      <c r="F10" s="44" t="inlineStr">
         <is>
           <t>□ 热身
 □ 3分钟耐力跳绳
@@ -3066,7 +3097,7 @@
 □ 放松拉伸</t>
         </is>
       </c>
-      <c r="G10" s="41" t="inlineStr">
+      <c r="G10" s="44" t="inlineStr">
         <is>
           <t>□ 热身
 □ 耐力跑2公里
@@ -3075,17 +3106,17 @@
 □ 放松拉伸</t>
         </is>
       </c>
-      <c r="H10" s="33" t="inlineStr">
+      <c r="H10" s="45" t="inlineStr">
         <is>
           <t>休息 · 自由活动</t>
         </is>
       </c>
-      <c r="I10" s="33" t="inlineStr">
+      <c r="I10" s="45" t="inlineStr">
         <is>
           <t>休息 · 自由活动</t>
         </is>
       </c>
-      <c r="J10" s="42" t="inlineStr">
+      <c r="J10" s="46" t="inlineStr">
         <is>
           <t>目标:跳绳200个/分钟;仰卧起坐49个/分钟;体前屈膝盖伸直、手指过脚尖;有条件可加练加速跑</t>
         </is>
@@ -3093,47 +3124,47 @@
     </row>
     <row r="11" ht="50.4" customHeight="1">
       <c r="A11" s="15" t="n"/>
-      <c r="B11" s="40" t="inlineStr">
+      <c r="B11" s="44" t="inlineStr">
         <is>
           <t>成绩记录(把当天成绩写进括号)</t>
         </is>
       </c>
-      <c r="C11" s="41" t="inlineStr">
+      <c r="C11" s="47" t="inlineStr">
         <is>
           <t>(        )</t>
         </is>
       </c>
-      <c r="D11" s="41" t="inlineStr">
+      <c r="D11" s="47" t="inlineStr">
         <is>
           <t>(        )</t>
         </is>
       </c>
-      <c r="E11" s="41" t="inlineStr">
+      <c r="E11" s="47" t="inlineStr">
         <is>
           <t>(        )</t>
         </is>
       </c>
-      <c r="F11" s="41" t="inlineStr">
+      <c r="F11" s="47" t="inlineStr">
         <is>
           <t>(        )</t>
         </is>
       </c>
-      <c r="G11" s="41" t="inlineStr">
+      <c r="G11" s="47" t="inlineStr">
         <is>
           <t>(        )</t>
         </is>
       </c>
-      <c r="H11" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I11" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J11" s="42" t="inlineStr">
+      <c r="H11" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I11" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J11" s="46" t="inlineStr">
         <is>
           <t>开学交任务单,学校按完成情况评优体奖章</t>
         </is>
@@ -3141,39 +3172,39 @@
     </row>
     <row r="12" ht="50.4" customHeight="1">
       <c r="A12" s="15" t="n"/>
-      <c r="B12" s="43" t="inlineStr">
+      <c r="B12" s="48" t="inlineStr">
         <is>
           <t>家长点评签字(每周一次)</t>
         </is>
       </c>
-      <c r="C12" s="44" t="inlineStr"/>
-      <c r="D12" s="44" t="n"/>
-      <c r="E12" s="44" t="n"/>
-      <c r="F12" s="44" t="n"/>
-      <c r="G12" s="44" t="n"/>
-      <c r="H12" s="44" t="n"/>
-      <c r="I12" s="44" t="n"/>
-      <c r="J12" s="42" t="inlineStr">
+      <c r="C12" s="49" t="inlineStr"/>
+      <c r="D12" s="49" t="n"/>
+      <c r="E12" s="49" t="n"/>
+      <c r="F12" s="49" t="n"/>
+      <c r="G12" s="49" t="n"/>
+      <c r="H12" s="49" t="n"/>
+      <c r="I12" s="49" t="n"/>
+      <c r="J12" s="46" t="inlineStr">
         <is>
           <t>对应任务单“家长点评签字”栏</t>
         </is>
       </c>
     </row>
     <row r="13" ht="50.4" customHeight="1">
-      <c r="A13" s="45" t="inlineStr">
+      <c r="A13" s="50" t="inlineStr">
         <is>
           <t>★ 英语作业不含周六日和法定节假日 · 体育锻炼注意防暑降温 · 数学实践作业4选2(本表建议做③气温统计、④密铺图案,也可换成①数学游戏、②小区调查)</t>
         </is>
       </c>
-      <c r="B13" s="46" t="n"/>
-      <c r="C13" s="46" t="n"/>
-      <c r="D13" s="46" t="n"/>
-      <c r="E13" s="46" t="n"/>
-      <c r="F13" s="46" t="n"/>
-      <c r="G13" s="46" t="n"/>
-      <c r="H13" s="46" t="n"/>
-      <c r="I13" s="46" t="n"/>
-      <c r="J13" s="46" t="n"/>
+      <c r="B13" s="51" t="n"/>
+      <c r="C13" s="51" t="n"/>
+      <c r="D13" s="51" t="n"/>
+      <c r="E13" s="51" t="n"/>
+      <c r="F13" s="51" t="n"/>
+      <c r="G13" s="51" t="n"/>
+      <c r="H13" s="51" t="n"/>
+      <c r="I13" s="51" t="n"/>
+      <c r="J13" s="51" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -3214,118 +3245,118 @@
   </cols>
   <sheetData>
     <row r="1" ht="53.9" customHeight="1">
-      <c r="A1" s="27" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>四年级暑假每日安排 · 第4周(8月3日—8月9日)    完成一项在□里打✓</t>
         </is>
       </c>
     </row>
     <row r="2" ht="53.9" customHeight="1">
-      <c r="A2" s="28" t="inlineStr">
+      <c r="A2" s="31" t="inlineStr">
         <is>
           <t>科目</t>
         </is>
       </c>
-      <c r="B2" s="28" t="inlineStr">
+      <c r="B2" s="31" t="inlineStr">
         <is>
           <t>任务内容</t>
         </is>
       </c>
-      <c r="C2" s="28" t="inlineStr">
+      <c r="C2" s="31" t="inlineStr">
         <is>
           <t>周一
 8月3日</t>
         </is>
       </c>
-      <c r="D2" s="28" t="inlineStr">
+      <c r="D2" s="31" t="inlineStr">
         <is>
           <t>周二
 8月4日</t>
         </is>
       </c>
-      <c r="E2" s="28" t="inlineStr">
+      <c r="E2" s="31" t="inlineStr">
         <is>
           <t>周三
 8月5日</t>
         </is>
       </c>
-      <c r="F2" s="28" t="inlineStr">
+      <c r="F2" s="31" t="inlineStr">
         <is>
           <t>周四
 8月6日</t>
         </is>
       </c>
-      <c r="G2" s="28" t="inlineStr">
+      <c r="G2" s="31" t="inlineStr">
         <is>
           <t>周五
 8月7日</t>
         </is>
       </c>
-      <c r="H2" s="29" t="inlineStr">
+      <c r="H2" s="32" t="inlineStr">
         <is>
           <t>周六
 8月8日</t>
         </is>
       </c>
-      <c r="I2" s="29" t="inlineStr">
+      <c r="I2" s="32" t="inlineStr">
         <is>
           <t>周日
 8月9日</t>
         </is>
       </c>
-      <c r="J2" s="28" t="inlineStr">
+      <c r="J2" s="31" t="inlineStr">
         <is>
           <t>要求 / 备注</t>
         </is>
       </c>
     </row>
     <row r="3" ht="43.1" customHeight="1">
-      <c r="A3" s="30" t="inlineStr">
+      <c r="A3" s="33" t="inlineStr">
         <is>
           <t>数学</t>
         </is>
       </c>
-      <c r="B3" s="31" t="inlineStr">
+      <c r="B3" s="34" t="inlineStr">
         <is>
           <t>口算 15~20 道(题目自备)</t>
         </is>
       </c>
-      <c r="C3" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="D3" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="E3" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="F3" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="G3" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="H3" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I3" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J3" s="34" t="inlineStr">
+      <c r="C3" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="D3" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="E3" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="F3" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="G3" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="H3" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I3" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J3" s="37" t="inlineStr">
         <is>
           <t>每日基础练习</t>
         </is>
@@ -3333,47 +3364,47 @@
     </row>
     <row r="4" ht="43.1" customHeight="1">
       <c r="A4" s="3" t="n"/>
-      <c r="B4" s="31" t="inlineStr">
+      <c r="B4" s="34" t="inlineStr">
         <is>
           <t>计算 4 道:三位数÷两位数 2道 + 小数乘法 2道</t>
         </is>
       </c>
-      <c r="C4" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="D4" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="E4" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="F4" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="G4" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="H4" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I4" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J4" s="34" t="inlineStr">
+      <c r="C4" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="D4" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="E4" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="F4" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="G4" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="H4" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I4" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J4" s="37" t="inlineStr">
         <is>
           <t>每日基础练习</t>
         </is>
@@ -3381,47 +3412,47 @@
     </row>
     <row r="5" ht="50.3" customHeight="1">
       <c r="A5" s="3" t="n"/>
-      <c r="B5" s="31" t="inlineStr">
+      <c r="B5" s="34" t="inlineStr">
         <is>
           <t>综合练习卷(每周1~2份,按8周计)</t>
         </is>
       </c>
-      <c r="C5" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D5" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E5" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H5" s="32" t="inlineStr">
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" s="35" t="inlineStr">
         <is>
           <t>□ 第4份(必做)</t>
         </is>
       </c>
-      <c r="I5" s="32" t="inlineStr">
+      <c r="I5" s="35" t="inlineStr">
         <is>
           <t>□ 加练1份(选做)</t>
         </is>
       </c>
-      <c r="J5" s="34" t="inlineStr">
+      <c r="J5" s="37" t="inlineStr">
         <is>
           <t>三选一:①数练活页卷 ②《5.3全优卷》剩余试卷 ③自备练习卷</t>
         </is>
@@ -3429,47 +3460,47 @@
     </row>
     <row r="6" ht="57.5" customHeight="1">
       <c r="A6" s="3" t="n"/>
-      <c r="B6" s="47" t="inlineStr">
+      <c r="B6" s="52" t="inlineStr">
         <is>
           <t>实践作业(原单第③项):统计一周(7天)气温</t>
         </is>
       </c>
-      <c r="C6" s="48" t="inlineStr">
+      <c r="C6" s="53" t="inlineStr">
         <is>
           <t>□ 记当天气温</t>
         </is>
       </c>
-      <c r="D6" s="48" t="inlineStr">
+      <c r="D6" s="53" t="inlineStr">
         <is>
           <t>□ 记当天气温</t>
         </is>
       </c>
-      <c r="E6" s="48" t="inlineStr">
+      <c r="E6" s="53" t="inlineStr">
         <is>
           <t>□ 记当天气温</t>
         </is>
       </c>
-      <c r="F6" s="48" t="inlineStr">
+      <c r="F6" s="53" t="inlineStr">
         <is>
           <t>□ 记当天气温</t>
         </is>
       </c>
-      <c r="G6" s="48" t="inlineStr">
+      <c r="G6" s="53" t="inlineStr">
         <is>
           <t>□ 记当天气温</t>
         </is>
       </c>
-      <c r="H6" s="48" t="inlineStr">
+      <c r="H6" s="53" t="inlineStr">
         <is>
           <t>□ 记当天气温</t>
         </is>
       </c>
-      <c r="I6" s="48" t="inlineStr">
+      <c r="I6" s="53" t="inlineStr">
         <is>
           <t>□ 记气温+绘统计图,提数学问题并解答</t>
         </is>
       </c>
-      <c r="J6" s="49" t="inlineStr">
+      <c r="J6" s="54" t="inlineStr">
         <is>
           <t>A4纸完成,配表格/照片(实践4选2之一)</t>
         </is>
@@ -3477,12 +3508,12 @@
     </row>
     <row r="7" ht="35.9" customHeight="1">
       <c r="A7" s="3" t="n"/>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>选做:《教材全解》拓展题 / 与家长商定提高内容</t>
         </is>
       </c>
-      <c r="C7" s="32" t="inlineStr">
+      <c r="C7" s="38" t="inlineStr">
         <is>
           <t>学有余力时安排,不做硬性打卡</t>
         </is>
@@ -3493,59 +3524,59 @@
       <c r="G7" s="5" t="n"/>
       <c r="H7" s="5" t="n"/>
       <c r="I7" s="5" t="n"/>
-      <c r="J7" s="34" t="inlineStr">
+      <c r="J7" s="37" t="inlineStr">
         <is>
           <t>自行安排</t>
         </is>
       </c>
     </row>
     <row r="8" ht="43.1" customHeight="1">
-      <c r="A8" s="35" t="inlineStr">
+      <c r="A8" s="39" t="inlineStr">
         <is>
           <t>英语</t>
         </is>
       </c>
-      <c r="B8" s="36" t="inlineStr">
+      <c r="B8" s="40" t="inlineStr">
         <is>
           <t>必做① 每天大声朗读三下课本(每次5分钟)</t>
         </is>
       </c>
-      <c r="C8" s="37" t="inlineStr">
+      <c r="C8" s="41" t="inlineStr">
         <is>
           <t>□ 5分钟</t>
         </is>
       </c>
-      <c r="D8" s="37" t="inlineStr">
+      <c r="D8" s="41" t="inlineStr">
         <is>
           <t>□ 5分钟</t>
         </is>
       </c>
-      <c r="E8" s="37" t="inlineStr">
+      <c r="E8" s="41" t="inlineStr">
         <is>
           <t>□ 5分钟</t>
         </is>
       </c>
-      <c r="F8" s="37" t="inlineStr">
+      <c r="F8" s="41" t="inlineStr">
         <is>
           <t>□ 5分钟</t>
         </is>
       </c>
-      <c r="G8" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H8" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I8" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J8" s="38" t="inlineStr">
+      <c r="G8" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J8" s="42" t="inlineStr">
         <is>
           <t>全假期共24次;第1~6周每周4次(本周为第13~16次)</t>
         </is>
@@ -3553,47 +3584,47 @@
     </row>
     <row r="9" ht="43.1" customHeight="1">
       <c r="A9" s="9" t="n"/>
-      <c r="B9" s="36" t="inlineStr">
+      <c r="B9" s="40" t="inlineStr">
         <is>
           <t>必做② 抄写四上&amp;四下单词/词组并造句(每次10分钟)</t>
         </is>
       </c>
-      <c r="C9" s="37" t="inlineStr">
+      <c r="C9" s="41" t="inlineStr">
         <is>
           <t>□ 10分钟</t>
         </is>
       </c>
-      <c r="D9" s="37" t="inlineStr">
+      <c r="D9" s="41" t="inlineStr">
         <is>
           <t>□ 10分钟</t>
         </is>
       </c>
-      <c r="E9" s="37" t="inlineStr">
+      <c r="E9" s="41" t="inlineStr">
         <is>
           <t>□ 10分钟</t>
         </is>
       </c>
-      <c r="F9" s="37" t="inlineStr">
+      <c r="F9" s="41" t="inlineStr">
         <is>
           <t>□ 10分钟</t>
         </is>
       </c>
-      <c r="G9" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H9" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I9" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J9" s="38" t="inlineStr">
+      <c r="G9" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I9" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J9" s="42" t="inlineStr">
         <is>
           <t>全假期共24次;第1~6周每周4次</t>
         </is>
@@ -3601,64 +3632,64 @@
     </row>
     <row r="10" ht="43.1" customHeight="1">
       <c r="A10" s="9" t="n"/>
-      <c r="B10" s="36" t="inlineStr">
+      <c r="B10" s="40" t="inlineStr">
         <is>
           <t>必做③ 完成英语阅读题3篇(每次15分钟)</t>
         </is>
       </c>
-      <c r="C10" s="37" t="inlineStr">
+      <c r="C10" s="41" t="inlineStr">
         <is>
           <t>□ 3篇</t>
         </is>
       </c>
-      <c r="D10" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E10" s="37" t="inlineStr">
+      <c r="D10" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" s="41" t="inlineStr">
         <is>
           <t>□ 3篇</t>
         </is>
       </c>
-      <c r="F10" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="37" t="inlineStr">
+      <c r="F10" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="41" t="inlineStr">
         <is>
           <t>□ 3篇</t>
         </is>
       </c>
-      <c r="H10" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I10" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J10" s="38" t="inlineStr">
+      <c r="H10" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I10" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J10" s="42" t="inlineStr">
         <is>
           <t>全假期共15次;第1~5周每周一、三、五</t>
         </is>
       </c>
     </row>
     <row r="11" ht="172.5" customHeight="1">
-      <c r="A11" s="39" t="inlineStr">
+      <c r="A11" s="43" t="inlineStr">
         <is>
           <t>体育</t>
         </is>
       </c>
-      <c r="B11" s="40" t="inlineStr">
+      <c r="B11" s="44" t="inlineStr">
         <is>
           <t>每日锻炼(先热身 → 练习 → 放松拉伸)</t>
         </is>
       </c>
-      <c r="C11" s="41" t="inlineStr">
+      <c r="C11" s="44" t="inlineStr">
         <is>
           <t>□ 热身
 □ 1分钟计时跳绳×4组
@@ -3666,7 +3697,7 @@
 □ 坐位体前屈拉伸1分钟</t>
         </is>
       </c>
-      <c r="D11" s="41" t="inlineStr">
+      <c r="D11" s="44" t="inlineStr">
         <is>
           <t>□ 热身
 □ 跳绳200个/组×4组
@@ -3675,7 +3706,7 @@
 □ 坐位体前屈1分钟</t>
         </is>
       </c>
-      <c r="E11" s="41" t="inlineStr">
+      <c r="E11" s="44" t="inlineStr">
         <is>
           <t>□ 热身
 □ 1分钟计时跳绳×4组
@@ -3684,7 +3715,7 @@
 □ 放松拉伸</t>
         </is>
       </c>
-      <c r="F11" s="41" t="inlineStr">
+      <c r="F11" s="44" t="inlineStr">
         <is>
           <t>□ 热身
 □ 3分钟耐力跳绳
@@ -3692,7 +3723,7 @@
 □ 放松拉伸</t>
         </is>
       </c>
-      <c r="G11" s="41" t="inlineStr">
+      <c r="G11" s="44" t="inlineStr">
         <is>
           <t>□ 热身
 □ 耐力跑2公里
@@ -3701,17 +3732,17 @@
 □ 放松拉伸</t>
         </is>
       </c>
-      <c r="H11" s="33" t="inlineStr">
+      <c r="H11" s="45" t="inlineStr">
         <is>
           <t>休息 · 自由活动</t>
         </is>
       </c>
-      <c r="I11" s="33" t="inlineStr">
+      <c r="I11" s="45" t="inlineStr">
         <is>
           <t>休息 · 自由活动</t>
         </is>
       </c>
-      <c r="J11" s="42" t="inlineStr">
+      <c r="J11" s="46" t="inlineStr">
         <is>
           <t>目标:跳绳200个/分钟;仰卧起坐49个/分钟;体前屈膝盖伸直、手指过脚尖;有条件可加练加速跑</t>
         </is>
@@ -3719,47 +3750,47 @@
     </row>
     <row r="12" ht="46.7" customHeight="1">
       <c r="A12" s="15" t="n"/>
-      <c r="B12" s="40" t="inlineStr">
+      <c r="B12" s="44" t="inlineStr">
         <is>
           <t>成绩记录(把当天成绩写进括号)</t>
         </is>
       </c>
-      <c r="C12" s="41" t="inlineStr">
+      <c r="C12" s="47" t="inlineStr">
         <is>
           <t>(        )</t>
         </is>
       </c>
-      <c r="D12" s="41" t="inlineStr">
+      <c r="D12" s="47" t="inlineStr">
         <is>
           <t>(        )</t>
         </is>
       </c>
-      <c r="E12" s="41" t="inlineStr">
+      <c r="E12" s="47" t="inlineStr">
         <is>
           <t>(        )</t>
         </is>
       </c>
-      <c r="F12" s="41" t="inlineStr">
+      <c r="F12" s="47" t="inlineStr">
         <is>
           <t>(        )</t>
         </is>
       </c>
-      <c r="G12" s="41" t="inlineStr">
+      <c r="G12" s="47" t="inlineStr">
         <is>
           <t>(        )</t>
         </is>
       </c>
-      <c r="H12" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I12" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J12" s="42" t="inlineStr">
+      <c r="H12" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I12" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J12" s="46" t="inlineStr">
         <is>
           <t>开学交任务单,学校按完成情况评优体奖章</t>
         </is>
@@ -3767,39 +3798,39 @@
     </row>
     <row r="13" ht="46.7" customHeight="1">
       <c r="A13" s="15" t="n"/>
-      <c r="B13" s="43" t="inlineStr">
+      <c r="B13" s="48" t="inlineStr">
         <is>
           <t>家长点评签字(每周一次)</t>
         </is>
       </c>
-      <c r="C13" s="44" t="inlineStr"/>
-      <c r="D13" s="44" t="n"/>
-      <c r="E13" s="44" t="n"/>
-      <c r="F13" s="44" t="n"/>
-      <c r="G13" s="44" t="n"/>
-      <c r="H13" s="44" t="n"/>
-      <c r="I13" s="44" t="n"/>
-      <c r="J13" s="42" t="inlineStr">
+      <c r="C13" s="49" t="inlineStr"/>
+      <c r="D13" s="49" t="n"/>
+      <c r="E13" s="49" t="n"/>
+      <c r="F13" s="49" t="n"/>
+      <c r="G13" s="49" t="n"/>
+      <c r="H13" s="49" t="n"/>
+      <c r="I13" s="49" t="n"/>
+      <c r="J13" s="46" t="inlineStr">
         <is>
           <t>对应任务单“家长点评签字”栏</t>
         </is>
       </c>
     </row>
     <row r="14" ht="46.7" customHeight="1">
-      <c r="A14" s="45" t="inlineStr">
+      <c r="A14" s="50" t="inlineStr">
         <is>
           <t>★ 英语作业不含周六日和法定节假日 · 体育锻炼注意防暑降温 · 数学实践作业4选2(本表建议做③气温统计、④密铺图案,也可换成①数学游戏、②小区调查)</t>
         </is>
       </c>
-      <c r="B14" s="46" t="n"/>
-      <c r="C14" s="46" t="n"/>
-      <c r="D14" s="46" t="n"/>
-      <c r="E14" s="46" t="n"/>
-      <c r="F14" s="46" t="n"/>
-      <c r="G14" s="46" t="n"/>
-      <c r="H14" s="46" t="n"/>
-      <c r="I14" s="46" t="n"/>
-      <c r="J14" s="46" t="n"/>
+      <c r="B14" s="51" t="n"/>
+      <c r="C14" s="51" t="n"/>
+      <c r="D14" s="51" t="n"/>
+      <c r="E14" s="51" t="n"/>
+      <c r="F14" s="51" t="n"/>
+      <c r="G14" s="51" t="n"/>
+      <c r="H14" s="51" t="n"/>
+      <c r="I14" s="51" t="n"/>
+      <c r="J14" s="51" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -3840,118 +3871,118 @@
   </cols>
   <sheetData>
     <row r="1" ht="54.9" customHeight="1">
-      <c r="A1" s="27" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>四年级暑假每日安排 · 第5周(8月10日—8月16日)    完成一项在□里打✓</t>
         </is>
       </c>
     </row>
     <row r="2" ht="54.9" customHeight="1">
-      <c r="A2" s="28" t="inlineStr">
+      <c r="A2" s="31" t="inlineStr">
         <is>
           <t>科目</t>
         </is>
       </c>
-      <c r="B2" s="28" t="inlineStr">
+      <c r="B2" s="31" t="inlineStr">
         <is>
           <t>任务内容</t>
         </is>
       </c>
-      <c r="C2" s="28" t="inlineStr">
+      <c r="C2" s="31" t="inlineStr">
         <is>
           <t>周一
 8月10日</t>
         </is>
       </c>
-      <c r="D2" s="28" t="inlineStr">
+      <c r="D2" s="31" t="inlineStr">
         <is>
           <t>周二
 8月11日</t>
         </is>
       </c>
-      <c r="E2" s="28" t="inlineStr">
+      <c r="E2" s="31" t="inlineStr">
         <is>
           <t>周三
 8月12日</t>
         </is>
       </c>
-      <c r="F2" s="28" t="inlineStr">
+      <c r="F2" s="31" t="inlineStr">
         <is>
           <t>周四
 8月13日</t>
         </is>
       </c>
-      <c r="G2" s="28" t="inlineStr">
+      <c r="G2" s="31" t="inlineStr">
         <is>
           <t>周五
 8月14日</t>
         </is>
       </c>
-      <c r="H2" s="29" t="inlineStr">
+      <c r="H2" s="32" t="inlineStr">
         <is>
           <t>周六
 8月15日</t>
         </is>
       </c>
-      <c r="I2" s="29" t="inlineStr">
+      <c r="I2" s="32" t="inlineStr">
         <is>
           <t>周日
 8月16日</t>
         </is>
       </c>
-      <c r="J2" s="28" t="inlineStr">
+      <c r="J2" s="31" t="inlineStr">
         <is>
           <t>要求 / 备注</t>
         </is>
       </c>
     </row>
     <row r="3" ht="43.9" customHeight="1">
-      <c r="A3" s="30" t="inlineStr">
+      <c r="A3" s="33" t="inlineStr">
         <is>
           <t>数学</t>
         </is>
       </c>
-      <c r="B3" s="31" t="inlineStr">
+      <c r="B3" s="34" t="inlineStr">
         <is>
           <t>口算 15~20 道(题目自备)</t>
         </is>
       </c>
-      <c r="C3" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="D3" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="E3" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="F3" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="G3" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="H3" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I3" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J3" s="34" t="inlineStr">
+      <c r="C3" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="D3" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="E3" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="F3" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="G3" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="H3" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I3" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J3" s="37" t="inlineStr">
         <is>
           <t>每日基础练习</t>
         </is>
@@ -3959,47 +3990,47 @@
     </row>
     <row r="4" ht="43.9" customHeight="1">
       <c r="A4" s="3" t="n"/>
-      <c r="B4" s="31" t="inlineStr">
+      <c r="B4" s="34" t="inlineStr">
         <is>
           <t>计算 4 道:三位数÷两位数 2道 + 小数乘法 2道</t>
         </is>
       </c>
-      <c r="C4" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="D4" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="E4" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="F4" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="G4" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="H4" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I4" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J4" s="34" t="inlineStr">
+      <c r="C4" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="D4" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="E4" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="F4" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="G4" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="H4" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I4" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J4" s="37" t="inlineStr">
         <is>
           <t>每日基础练习</t>
         </is>
@@ -4007,47 +4038,47 @@
     </row>
     <row r="5" ht="51.3" customHeight="1">
       <c r="A5" s="3" t="n"/>
-      <c r="B5" s="31" t="inlineStr">
+      <c r="B5" s="34" t="inlineStr">
         <is>
           <t>综合练习卷(每周1~2份,按8周计)</t>
         </is>
       </c>
-      <c r="C5" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D5" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E5" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H5" s="32" t="inlineStr">
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" s="35" t="inlineStr">
         <is>
           <t>□ 第5份(必做)</t>
         </is>
       </c>
-      <c r="I5" s="32" t="inlineStr">
+      <c r="I5" s="35" t="inlineStr">
         <is>
           <t>□ 加练1份(选做)</t>
         </is>
       </c>
-      <c r="J5" s="34" t="inlineStr">
+      <c r="J5" s="37" t="inlineStr">
         <is>
           <t>三选一:①数练活页卷 ②《5.3全优卷》剩余试卷 ③自备练习卷</t>
         </is>
@@ -4055,12 +4086,12 @@
     </row>
     <row r="6" ht="36.6" customHeight="1">
       <c r="A6" s="3" t="n"/>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>选做:《教材全解》拓展题 / 与家长商定提高内容</t>
         </is>
       </c>
-      <c r="C6" s="32" t="inlineStr">
+      <c r="C6" s="38" t="inlineStr">
         <is>
           <t>学有余力时安排,不做硬性打卡</t>
         </is>
@@ -4071,59 +4102,59 @@
       <c r="G6" s="5" t="n"/>
       <c r="H6" s="5" t="n"/>
       <c r="I6" s="5" t="n"/>
-      <c r="J6" s="34" t="inlineStr">
+      <c r="J6" s="37" t="inlineStr">
         <is>
           <t>自行安排</t>
         </is>
       </c>
     </row>
     <row r="7" ht="43.9" customHeight="1">
-      <c r="A7" s="35" t="inlineStr">
+      <c r="A7" s="39" t="inlineStr">
         <is>
           <t>英语</t>
         </is>
       </c>
-      <c r="B7" s="36" t="inlineStr">
+      <c r="B7" s="40" t="inlineStr">
         <is>
           <t>必做① 每天大声朗读三下课本(每次5分钟)</t>
         </is>
       </c>
-      <c r="C7" s="37" t="inlineStr">
+      <c r="C7" s="41" t="inlineStr">
         <is>
           <t>□ 5分钟</t>
         </is>
       </c>
-      <c r="D7" s="37" t="inlineStr">
+      <c r="D7" s="41" t="inlineStr">
         <is>
           <t>□ 5分钟</t>
         </is>
       </c>
-      <c r="E7" s="37" t="inlineStr">
+      <c r="E7" s="41" t="inlineStr">
         <is>
           <t>□ 5分钟</t>
         </is>
       </c>
-      <c r="F7" s="37" t="inlineStr">
+      <c r="F7" s="41" t="inlineStr">
         <is>
           <t>□ 5分钟</t>
         </is>
       </c>
-      <c r="G7" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H7" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I7" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J7" s="38" t="inlineStr">
+      <c r="G7" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I7" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J7" s="42" t="inlineStr">
         <is>
           <t>全假期共24次;第1~6周每周4次(本周为第17~20次)</t>
         </is>
@@ -4131,47 +4162,47 @@
     </row>
     <row r="8" ht="43.9" customHeight="1">
       <c r="A8" s="9" t="n"/>
-      <c r="B8" s="36" t="inlineStr">
+      <c r="B8" s="40" t="inlineStr">
         <is>
           <t>必做② 抄写四上&amp;四下单词/词组并造句(每次10分钟)</t>
         </is>
       </c>
-      <c r="C8" s="37" t="inlineStr">
+      <c r="C8" s="41" t="inlineStr">
         <is>
           <t>□ 10分钟</t>
         </is>
       </c>
-      <c r="D8" s="37" t="inlineStr">
+      <c r="D8" s="41" t="inlineStr">
         <is>
           <t>□ 10分钟</t>
         </is>
       </c>
-      <c r="E8" s="37" t="inlineStr">
+      <c r="E8" s="41" t="inlineStr">
         <is>
           <t>□ 10分钟</t>
         </is>
       </c>
-      <c r="F8" s="37" t="inlineStr">
+      <c r="F8" s="41" t="inlineStr">
         <is>
           <t>□ 10分钟</t>
         </is>
       </c>
-      <c r="G8" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H8" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I8" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J8" s="38" t="inlineStr">
+      <c r="G8" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J8" s="42" t="inlineStr">
         <is>
           <t>全假期共24次;第1~6周每周4次</t>
         </is>
@@ -4179,47 +4210,47 @@
     </row>
     <row r="9" ht="43.9" customHeight="1">
       <c r="A9" s="9" t="n"/>
-      <c r="B9" s="36" t="inlineStr">
+      <c r="B9" s="40" t="inlineStr">
         <is>
           <t>必做③ 完成英语阅读题3篇(每次15分钟)</t>
         </is>
       </c>
-      <c r="C9" s="37" t="inlineStr">
+      <c r="C9" s="41" t="inlineStr">
         <is>
           <t>□ 3篇</t>
         </is>
       </c>
-      <c r="D9" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E9" s="37" t="inlineStr">
+      <c r="D9" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="41" t="inlineStr">
         <is>
           <t>□ 3篇</t>
         </is>
       </c>
-      <c r="F9" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G9" s="37" t="inlineStr">
+      <c r="F9" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="41" t="inlineStr">
         <is>
           <t>□ 3篇</t>
         </is>
       </c>
-      <c r="H9" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I9" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J9" s="38" t="inlineStr">
+      <c r="H9" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I9" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J9" s="42" t="inlineStr">
         <is>
           <t>全假期共15次;第1~5周每周一、三、五</t>
         </is>
@@ -4227,64 +4258,64 @@
     </row>
     <row r="10" ht="43.9" customHeight="1">
       <c r="A10" s="9" t="n"/>
-      <c r="B10" s="36" t="inlineStr">
+      <c r="B10" s="40" t="inlineStr">
         <is>
           <t>选做① 学唱一首英文歌曲(歌曲自选,每次5分钟)</t>
         </is>
       </c>
-      <c r="C10" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D10" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E10" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="37" t="inlineStr">
+      <c r="C10" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="41" t="inlineStr">
         <is>
           <t>□ 5分钟</t>
         </is>
       </c>
-      <c r="H10" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I10" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J10" s="38" t="inlineStr">
+      <c r="H10" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I10" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J10" s="42" t="inlineStr">
         <is>
           <t>共2次(第5、6周各1次)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="175.8" customHeight="1">
-      <c r="A11" s="39" t="inlineStr">
+      <c r="A11" s="43" t="inlineStr">
         <is>
           <t>体育</t>
         </is>
       </c>
-      <c r="B11" s="40" t="inlineStr">
+      <c r="B11" s="44" t="inlineStr">
         <is>
           <t>每日锻炼(先热身 → 练习 → 放松拉伸)</t>
         </is>
       </c>
-      <c r="C11" s="41" t="inlineStr">
+      <c r="C11" s="44" t="inlineStr">
         <is>
           <t>□ 热身
 □ 1分钟计时跳绳×4组
@@ -4292,7 +4323,7 @@
 □ 坐位体前屈拉伸1分钟</t>
         </is>
       </c>
-      <c r="D11" s="41" t="inlineStr">
+      <c r="D11" s="44" t="inlineStr">
         <is>
           <t>□ 热身
 □ 跳绳200个/组×4组
@@ -4301,7 +4332,7 @@
 □ 坐位体前屈1分钟</t>
         </is>
       </c>
-      <c r="E11" s="41" t="inlineStr">
+      <c r="E11" s="44" t="inlineStr">
         <is>
           <t>□ 热身
 □ 1分钟计时跳绳×4组
@@ -4310,7 +4341,7 @@
 □ 放松拉伸</t>
         </is>
       </c>
-      <c r="F11" s="41" t="inlineStr">
+      <c r="F11" s="44" t="inlineStr">
         <is>
           <t>□ 热身
 □ 3分钟耐力跳绳
@@ -4318,7 +4349,7 @@
 □ 放松拉伸</t>
         </is>
       </c>
-      <c r="G11" s="41" t="inlineStr">
+      <c r="G11" s="44" t="inlineStr">
         <is>
           <t>□ 热身
 □ 耐力跑2公里
@@ -4327,17 +4358,17 @@
 □ 放松拉伸</t>
         </is>
       </c>
-      <c r="H11" s="33" t="inlineStr">
+      <c r="H11" s="45" t="inlineStr">
         <is>
           <t>休息 · 自由活动</t>
         </is>
       </c>
-      <c r="I11" s="33" t="inlineStr">
+      <c r="I11" s="45" t="inlineStr">
         <is>
           <t>休息 · 自由活动</t>
         </is>
       </c>
-      <c r="J11" s="42" t="inlineStr">
+      <c r="J11" s="46" t="inlineStr">
         <is>
           <t>目标:跳绳200个/分钟;仰卧起坐49个/分钟;体前屈膝盖伸直、手指过脚尖;有条件可加练加速跑</t>
         </is>
@@ -4345,47 +4376,47 @@
     </row>
     <row r="12" ht="47.6" customHeight="1">
       <c r="A12" s="15" t="n"/>
-      <c r="B12" s="40" t="inlineStr">
+      <c r="B12" s="44" t="inlineStr">
         <is>
           <t>成绩记录(把当天成绩写进括号)</t>
         </is>
       </c>
-      <c r="C12" s="41" t="inlineStr">
+      <c r="C12" s="47" t="inlineStr">
         <is>
           <t>(        )</t>
         </is>
       </c>
-      <c r="D12" s="41" t="inlineStr">
+      <c r="D12" s="47" t="inlineStr">
         <is>
           <t>(        )</t>
         </is>
       </c>
-      <c r="E12" s="41" t="inlineStr">
+      <c r="E12" s="47" t="inlineStr">
         <is>
           <t>(        )</t>
         </is>
       </c>
-      <c r="F12" s="41" t="inlineStr">
+      <c r="F12" s="47" t="inlineStr">
         <is>
           <t>(        )</t>
         </is>
       </c>
-      <c r="G12" s="41" t="inlineStr">
+      <c r="G12" s="47" t="inlineStr">
         <is>
           <t>(        )</t>
         </is>
       </c>
-      <c r="H12" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I12" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J12" s="42" t="inlineStr">
+      <c r="H12" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I12" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J12" s="46" t="inlineStr">
         <is>
           <t>开学交任务单,学校按完成情况评优体奖章</t>
         </is>
@@ -4393,39 +4424,39 @@
     </row>
     <row r="13" ht="47.6" customHeight="1">
       <c r="A13" s="15" t="n"/>
-      <c r="B13" s="43" t="inlineStr">
+      <c r="B13" s="48" t="inlineStr">
         <is>
           <t>家长点评签字(每周一次)</t>
         </is>
       </c>
-      <c r="C13" s="44" t="inlineStr"/>
-      <c r="D13" s="44" t="n"/>
-      <c r="E13" s="44" t="n"/>
-      <c r="F13" s="44" t="n"/>
-      <c r="G13" s="44" t="n"/>
-      <c r="H13" s="44" t="n"/>
-      <c r="I13" s="44" t="n"/>
-      <c r="J13" s="42" t="inlineStr">
+      <c r="C13" s="49" t="inlineStr"/>
+      <c r="D13" s="49" t="n"/>
+      <c r="E13" s="49" t="n"/>
+      <c r="F13" s="49" t="n"/>
+      <c r="G13" s="49" t="n"/>
+      <c r="H13" s="49" t="n"/>
+      <c r="I13" s="49" t="n"/>
+      <c r="J13" s="46" t="inlineStr">
         <is>
           <t>对应任务单“家长点评签字”栏</t>
         </is>
       </c>
     </row>
     <row r="14" ht="47.6" customHeight="1">
-      <c r="A14" s="45" t="inlineStr">
+      <c r="A14" s="50" t="inlineStr">
         <is>
           <t>★ 英语作业不含周六日和法定节假日 · 体育锻炼注意防暑降温 · 数学实践作业4选2(本表建议做③气温统计、④密铺图案,也可换成①数学游戏、②小区调查)</t>
         </is>
       </c>
-      <c r="B14" s="46" t="n"/>
-      <c r="C14" s="46" t="n"/>
-      <c r="D14" s="46" t="n"/>
-      <c r="E14" s="46" t="n"/>
-      <c r="F14" s="46" t="n"/>
-      <c r="G14" s="46" t="n"/>
-      <c r="H14" s="46" t="n"/>
-      <c r="I14" s="46" t="n"/>
-      <c r="J14" s="46" t="n"/>
+      <c r="B14" s="51" t="n"/>
+      <c r="C14" s="51" t="n"/>
+      <c r="D14" s="51" t="n"/>
+      <c r="E14" s="51" t="n"/>
+      <c r="F14" s="51" t="n"/>
+      <c r="G14" s="51" t="n"/>
+      <c r="H14" s="51" t="n"/>
+      <c r="I14" s="51" t="n"/>
+      <c r="J14" s="51" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -4466,118 +4497,118 @@
   </cols>
   <sheetData>
     <row r="1" ht="54.4" customHeight="1">
-      <c r="A1" s="27" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>四年级暑假每日安排 · 第6周(8月17日—8月23日)    完成一项在□里打✓</t>
         </is>
       </c>
     </row>
     <row r="2" ht="54.4" customHeight="1">
-      <c r="A2" s="28" t="inlineStr">
+      <c r="A2" s="31" t="inlineStr">
         <is>
           <t>科目</t>
         </is>
       </c>
-      <c r="B2" s="28" t="inlineStr">
+      <c r="B2" s="31" t="inlineStr">
         <is>
           <t>任务内容</t>
         </is>
       </c>
-      <c r="C2" s="28" t="inlineStr">
+      <c r="C2" s="31" t="inlineStr">
         <is>
           <t>周一
 8月17日</t>
         </is>
       </c>
-      <c r="D2" s="28" t="inlineStr">
+      <c r="D2" s="31" t="inlineStr">
         <is>
           <t>周二
 8月18日</t>
         </is>
       </c>
-      <c r="E2" s="28" t="inlineStr">
+      <c r="E2" s="31" t="inlineStr">
         <is>
           <t>周三
 8月19日</t>
         </is>
       </c>
-      <c r="F2" s="28" t="inlineStr">
+      <c r="F2" s="31" t="inlineStr">
         <is>
           <t>周四
 8月20日</t>
         </is>
       </c>
-      <c r="G2" s="28" t="inlineStr">
+      <c r="G2" s="31" t="inlineStr">
         <is>
           <t>周五
 8月21日</t>
         </is>
       </c>
-      <c r="H2" s="29" t="inlineStr">
+      <c r="H2" s="32" t="inlineStr">
         <is>
           <t>周六
 8月22日</t>
         </is>
       </c>
-      <c r="I2" s="29" t="inlineStr">
+      <c r="I2" s="32" t="inlineStr">
         <is>
           <t>周日
 8月23日</t>
         </is>
       </c>
-      <c r="J2" s="28" t="inlineStr">
+      <c r="J2" s="31" t="inlineStr">
         <is>
           <t>要求 / 备注</t>
         </is>
       </c>
     </row>
     <row r="3" ht="43.5" customHeight="1">
-      <c r="A3" s="30" t="inlineStr">
+      <c r="A3" s="33" t="inlineStr">
         <is>
           <t>数学</t>
         </is>
       </c>
-      <c r="B3" s="31" t="inlineStr">
+      <c r="B3" s="34" t="inlineStr">
         <is>
           <t>口算 15~20 道(题目自备)</t>
         </is>
       </c>
-      <c r="C3" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="D3" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="E3" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="F3" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="G3" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="H3" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I3" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J3" s="34" t="inlineStr">
+      <c r="C3" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="D3" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="E3" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="F3" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="G3" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="H3" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I3" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J3" s="37" t="inlineStr">
         <is>
           <t>每日基础练习</t>
         </is>
@@ -4585,47 +4616,47 @@
     </row>
     <row r="4" ht="43.5" customHeight="1">
       <c r="A4" s="3" t="n"/>
-      <c r="B4" s="31" t="inlineStr">
+      <c r="B4" s="34" t="inlineStr">
         <is>
           <t>计算 4 道:三位数÷两位数 2道 + 小数乘法 2道</t>
         </is>
       </c>
-      <c r="C4" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="D4" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="E4" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="F4" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="G4" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="H4" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I4" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J4" s="34" t="inlineStr">
+      <c r="C4" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="D4" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="E4" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="F4" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="G4" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="H4" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I4" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J4" s="37" t="inlineStr">
         <is>
           <t>每日基础练习</t>
         </is>
@@ -4633,47 +4664,47 @@
     </row>
     <row r="5" ht="50.8" customHeight="1">
       <c r="A5" s="3" t="n"/>
-      <c r="B5" s="31" t="inlineStr">
+      <c r="B5" s="34" t="inlineStr">
         <is>
           <t>综合练习卷(每周1~2份,按8周计)</t>
         </is>
       </c>
-      <c r="C5" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D5" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E5" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H5" s="32" t="inlineStr">
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" s="35" t="inlineStr">
         <is>
           <t>□ 第6份(必做)</t>
         </is>
       </c>
-      <c r="I5" s="32" t="inlineStr">
+      <c r="I5" s="35" t="inlineStr">
         <is>
           <t>□ 加练1份(选做)</t>
         </is>
       </c>
-      <c r="J5" s="34" t="inlineStr">
+      <c r="J5" s="37" t="inlineStr">
         <is>
           <t>三选一:①数练活页卷 ②《5.3全优卷》剩余试卷 ③自备练习卷</t>
         </is>
@@ -4681,47 +4712,47 @@
     </row>
     <row r="6" ht="50.8" customHeight="1">
       <c r="A6" s="3" t="n"/>
-      <c r="B6" s="47" t="inlineStr">
+      <c r="B6" s="52" t="inlineStr">
         <is>
           <t>实践作业(原单第④项):设计密铺图案</t>
         </is>
       </c>
-      <c r="C6" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D6" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E6" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F6" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G6" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H6" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I6" s="48" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I6" s="53" t="inlineStr">
         <is>
           <t>□ 设计一幅美丽的密铺图案</t>
         </is>
       </c>
-      <c r="J6" s="49" t="inlineStr">
+      <c r="J6" s="54" t="inlineStr">
         <is>
           <t>一种图形或几种图形组合密铺,A4纸完成(实践4选2之二)</t>
         </is>
@@ -4729,12 +4760,12 @@
     </row>
     <row r="7" ht="36.3" customHeight="1">
       <c r="A7" s="3" t="n"/>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>选做:《教材全解》拓展题 / 与家长商定提高内容</t>
         </is>
       </c>
-      <c r="C7" s="32" t="inlineStr">
+      <c r="C7" s="38" t="inlineStr">
         <is>
           <t>学有余力时安排,不做硬性打卡</t>
         </is>
@@ -4745,59 +4776,59 @@
       <c r="G7" s="5" t="n"/>
       <c r="H7" s="5" t="n"/>
       <c r="I7" s="5" t="n"/>
-      <c r="J7" s="34" t="inlineStr">
+      <c r="J7" s="37" t="inlineStr">
         <is>
           <t>自行安排</t>
         </is>
       </c>
     </row>
     <row r="8" ht="43.5" customHeight="1">
-      <c r="A8" s="35" t="inlineStr">
+      <c r="A8" s="39" t="inlineStr">
         <is>
           <t>英语</t>
         </is>
       </c>
-      <c r="B8" s="36" t="inlineStr">
+      <c r="B8" s="40" t="inlineStr">
         <is>
           <t>必做① 每天大声朗读三下课本(每次5分钟)</t>
         </is>
       </c>
-      <c r="C8" s="37" t="inlineStr">
+      <c r="C8" s="41" t="inlineStr">
         <is>
           <t>□ 5分钟</t>
         </is>
       </c>
-      <c r="D8" s="37" t="inlineStr">
+      <c r="D8" s="41" t="inlineStr">
         <is>
           <t>□ 5分钟</t>
         </is>
       </c>
-      <c r="E8" s="37" t="inlineStr">
+      <c r="E8" s="41" t="inlineStr">
         <is>
           <t>□ 5分钟</t>
         </is>
       </c>
-      <c r="F8" s="37" t="inlineStr">
+      <c r="F8" s="41" t="inlineStr">
         <is>
           <t>□ 5分钟</t>
         </is>
       </c>
-      <c r="G8" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H8" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I8" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J8" s="38" t="inlineStr">
+      <c r="G8" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J8" s="42" t="inlineStr">
         <is>
           <t>全假期共24次;第1~6周每周4次(本周为第21~24次)</t>
         </is>
@@ -4805,47 +4836,47 @@
     </row>
     <row r="9" ht="43.5" customHeight="1">
       <c r="A9" s="9" t="n"/>
-      <c r="B9" s="36" t="inlineStr">
+      <c r="B9" s="40" t="inlineStr">
         <is>
           <t>必做② 抄写四上&amp;四下单词/词组并造句(每次10分钟)</t>
         </is>
       </c>
-      <c r="C9" s="37" t="inlineStr">
+      <c r="C9" s="41" t="inlineStr">
         <is>
           <t>□ 10分钟</t>
         </is>
       </c>
-      <c r="D9" s="37" t="inlineStr">
+      <c r="D9" s="41" t="inlineStr">
         <is>
           <t>□ 10分钟</t>
         </is>
       </c>
-      <c r="E9" s="37" t="inlineStr">
+      <c r="E9" s="41" t="inlineStr">
         <is>
           <t>□ 10分钟</t>
         </is>
       </c>
-      <c r="F9" s="37" t="inlineStr">
+      <c r="F9" s="41" t="inlineStr">
         <is>
           <t>□ 10分钟</t>
         </is>
       </c>
-      <c r="G9" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H9" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I9" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J9" s="38" t="inlineStr">
+      <c r="G9" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I9" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J9" s="42" t="inlineStr">
         <is>
           <t>全假期共24次;第1~6周每周4次</t>
         </is>
@@ -4853,64 +4884,64 @@
     </row>
     <row r="10" ht="43.5" customHeight="1">
       <c r="A10" s="9" t="n"/>
-      <c r="B10" s="36" t="inlineStr">
+      <c r="B10" s="40" t="inlineStr">
         <is>
           <t>选做① 学唱一首英文歌曲(歌曲自选,每次5分钟)</t>
         </is>
       </c>
-      <c r="C10" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D10" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E10" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="37" t="inlineStr">
+      <c r="C10" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="41" t="inlineStr">
         <is>
           <t>□ 5分钟</t>
         </is>
       </c>
-      <c r="H10" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I10" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J10" s="38" t="inlineStr">
+      <c r="H10" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I10" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J10" s="42" t="inlineStr">
         <is>
           <t>共2次(第5、6周各1次)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="174.1" customHeight="1">
-      <c r="A11" s="39" t="inlineStr">
+      <c r="A11" s="43" t="inlineStr">
         <is>
           <t>体育</t>
         </is>
       </c>
-      <c r="B11" s="40" t="inlineStr">
+      <c r="B11" s="44" t="inlineStr">
         <is>
           <t>每日锻炼(先热身 → 练习 → 放松拉伸)</t>
         </is>
       </c>
-      <c r="C11" s="41" t="inlineStr">
+      <c r="C11" s="44" t="inlineStr">
         <is>
           <t>□ 热身
 □ 1分钟计时跳绳×4组
@@ -4918,7 +4949,7 @@
 □ 坐位体前屈拉伸1分钟</t>
         </is>
       </c>
-      <c r="D11" s="41" t="inlineStr">
+      <c r="D11" s="44" t="inlineStr">
         <is>
           <t>□ 热身
 □ 跳绳200个/组×4组
@@ -4927,7 +4958,7 @@
 □ 坐位体前屈1分钟</t>
         </is>
       </c>
-      <c r="E11" s="41" t="inlineStr">
+      <c r="E11" s="44" t="inlineStr">
         <is>
           <t>□ 热身
 □ 1分钟计时跳绳×4组
@@ -4936,7 +4967,7 @@
 □ 放松拉伸</t>
         </is>
       </c>
-      <c r="F11" s="41" t="inlineStr">
+      <c r="F11" s="44" t="inlineStr">
         <is>
           <t>□ 热身
 □ 3分钟耐力跳绳
@@ -4944,7 +4975,7 @@
 □ 放松拉伸</t>
         </is>
       </c>
-      <c r="G11" s="41" t="inlineStr">
+      <c r="G11" s="44" t="inlineStr">
         <is>
           <t>□ 热身
 □ 耐力跑2公里
@@ -4953,17 +4984,17 @@
 □ 放松拉伸</t>
         </is>
       </c>
-      <c r="H11" s="33" t="inlineStr">
+      <c r="H11" s="45" t="inlineStr">
         <is>
           <t>休息 · 自由活动</t>
         </is>
       </c>
-      <c r="I11" s="33" t="inlineStr">
+      <c r="I11" s="45" t="inlineStr">
         <is>
           <t>休息 · 自由活动</t>
         </is>
       </c>
-      <c r="J11" s="42" t="inlineStr">
+      <c r="J11" s="46" t="inlineStr">
         <is>
           <t>目标:跳绳200个/分钟;仰卧起坐49个/分钟;体前屈膝盖伸直、手指过脚尖;有条件可加练加速跑</t>
         </is>
@@ -4971,47 +5002,47 @@
     </row>
     <row r="12" ht="47.2" customHeight="1">
       <c r="A12" s="15" t="n"/>
-      <c r="B12" s="40" t="inlineStr">
+      <c r="B12" s="44" t="inlineStr">
         <is>
           <t>成绩记录(把当天成绩写进括号)</t>
         </is>
       </c>
-      <c r="C12" s="41" t="inlineStr">
+      <c r="C12" s="47" t="inlineStr">
         <is>
           <t>(        )</t>
         </is>
       </c>
-      <c r="D12" s="41" t="inlineStr">
+      <c r="D12" s="47" t="inlineStr">
         <is>
           <t>(        )</t>
         </is>
       </c>
-      <c r="E12" s="41" t="inlineStr">
+      <c r="E12" s="47" t="inlineStr">
         <is>
           <t>(        )</t>
         </is>
       </c>
-      <c r="F12" s="41" t="inlineStr">
+      <c r="F12" s="47" t="inlineStr">
         <is>
           <t>(        )</t>
         </is>
       </c>
-      <c r="G12" s="41" t="inlineStr">
+      <c r="G12" s="47" t="inlineStr">
         <is>
           <t>(        )</t>
         </is>
       </c>
-      <c r="H12" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I12" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J12" s="42" t="inlineStr">
+      <c r="H12" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I12" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J12" s="46" t="inlineStr">
         <is>
           <t>开学交任务单,学校按完成情况评优体奖章</t>
         </is>
@@ -5019,39 +5050,39 @@
     </row>
     <row r="13" ht="47.2" customHeight="1">
       <c r="A13" s="15" t="n"/>
-      <c r="B13" s="43" t="inlineStr">
+      <c r="B13" s="48" t="inlineStr">
         <is>
           <t>家长点评签字(每周一次)</t>
         </is>
       </c>
-      <c r="C13" s="44" t="inlineStr"/>
-      <c r="D13" s="44" t="n"/>
-      <c r="E13" s="44" t="n"/>
-      <c r="F13" s="44" t="n"/>
-      <c r="G13" s="44" t="n"/>
-      <c r="H13" s="44" t="n"/>
-      <c r="I13" s="44" t="n"/>
-      <c r="J13" s="42" t="inlineStr">
+      <c r="C13" s="49" t="inlineStr"/>
+      <c r="D13" s="49" t="n"/>
+      <c r="E13" s="49" t="n"/>
+      <c r="F13" s="49" t="n"/>
+      <c r="G13" s="49" t="n"/>
+      <c r="H13" s="49" t="n"/>
+      <c r="I13" s="49" t="n"/>
+      <c r="J13" s="46" t="inlineStr">
         <is>
           <t>对应任务单“家长点评签字”栏</t>
         </is>
       </c>
     </row>
     <row r="14" ht="47.2" customHeight="1">
-      <c r="A14" s="45" t="inlineStr">
+      <c r="A14" s="50" t="inlineStr">
         <is>
           <t>★ 英语作业不含周六日和法定节假日 · 体育锻炼注意防暑降温 · 数学实践作业4选2(本表建议做③气温统计、④密铺图案,也可换成①数学游戏、②小区调查)</t>
         </is>
       </c>
-      <c r="B14" s="46" t="n"/>
-      <c r="C14" s="46" t="n"/>
-      <c r="D14" s="46" t="n"/>
-      <c r="E14" s="46" t="n"/>
-      <c r="F14" s="46" t="n"/>
-      <c r="G14" s="46" t="n"/>
-      <c r="H14" s="46" t="n"/>
-      <c r="I14" s="46" t="n"/>
-      <c r="J14" s="46" t="n"/>
+      <c r="B14" s="51" t="n"/>
+      <c r="C14" s="51" t="n"/>
+      <c r="D14" s="51" t="n"/>
+      <c r="E14" s="51" t="n"/>
+      <c r="F14" s="51" t="n"/>
+      <c r="G14" s="51" t="n"/>
+      <c r="H14" s="51" t="n"/>
+      <c r="I14" s="51" t="n"/>
+      <c r="J14" s="51" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -5092,118 +5123,118 @@
   </cols>
   <sheetData>
     <row r="1" ht="60" customHeight="1">
-      <c r="A1" s="27" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>四年级暑假每日安排 · 第7周(8月24日—8月30日)    完成一项在□里打✓</t>
         </is>
       </c>
     </row>
     <row r="2" ht="60" customHeight="1">
-      <c r="A2" s="28" t="inlineStr">
+      <c r="A2" s="31" t="inlineStr">
         <is>
           <t>科目</t>
         </is>
       </c>
-      <c r="B2" s="28" t="inlineStr">
+      <c r="B2" s="31" t="inlineStr">
         <is>
           <t>任务内容</t>
         </is>
       </c>
-      <c r="C2" s="28" t="inlineStr">
+      <c r="C2" s="31" t="inlineStr">
         <is>
           <t>周一
 8月24日</t>
         </is>
       </c>
-      <c r="D2" s="28" t="inlineStr">
+      <c r="D2" s="31" t="inlineStr">
         <is>
           <t>周二
 8月25日</t>
         </is>
       </c>
-      <c r="E2" s="28" t="inlineStr">
+      <c r="E2" s="31" t="inlineStr">
         <is>
           <t>周三
 8月26日</t>
         </is>
       </c>
-      <c r="F2" s="28" t="inlineStr">
+      <c r="F2" s="31" t="inlineStr">
         <is>
           <t>周四
 8月27日</t>
         </is>
       </c>
-      <c r="G2" s="28" t="inlineStr">
+      <c r="G2" s="31" t="inlineStr">
         <is>
           <t>周五
 8月28日</t>
         </is>
       </c>
-      <c r="H2" s="29" t="inlineStr">
+      <c r="H2" s="32" t="inlineStr">
         <is>
           <t>周六
 8月29日</t>
         </is>
       </c>
-      <c r="I2" s="29" t="inlineStr">
+      <c r="I2" s="32" t="inlineStr">
         <is>
           <t>周日
 8月30日</t>
         </is>
       </c>
-      <c r="J2" s="28" t="inlineStr">
+      <c r="J2" s="31" t="inlineStr">
         <is>
           <t>要求 / 备注</t>
         </is>
       </c>
     </row>
     <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="30" t="inlineStr">
+      <c r="A3" s="33" t="inlineStr">
         <is>
           <t>数学</t>
         </is>
       </c>
-      <c r="B3" s="31" t="inlineStr">
+      <c r="B3" s="34" t="inlineStr">
         <is>
           <t>口算 15~20 道(题目自备)</t>
         </is>
       </c>
-      <c r="C3" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="D3" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="E3" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="F3" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="G3" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="H3" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I3" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J3" s="34" t="inlineStr">
+      <c r="C3" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="D3" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="E3" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="F3" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="G3" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="H3" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I3" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J3" s="37" t="inlineStr">
         <is>
           <t>每日基础练习</t>
         </is>
@@ -5211,47 +5242,47 @@
     </row>
     <row r="4" ht="48" customHeight="1">
       <c r="A4" s="3" t="n"/>
-      <c r="B4" s="31" t="inlineStr">
+      <c r="B4" s="34" t="inlineStr">
         <is>
           <t>计算 4 道:三位数÷两位数 2道 + 小数乘法 2道</t>
         </is>
       </c>
-      <c r="C4" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="D4" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="E4" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="F4" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="G4" s="32" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="H4" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I4" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J4" s="34" t="inlineStr">
+      <c r="C4" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="D4" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="E4" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="F4" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="G4" s="35" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="H4" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I4" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J4" s="37" t="inlineStr">
         <is>
           <t>每日基础练习</t>
         </is>
@@ -5259,47 +5290,47 @@
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="3" t="n"/>
-      <c r="B5" s="31" t="inlineStr">
+      <c r="B5" s="34" t="inlineStr">
         <is>
           <t>综合练习卷(每周1~2份,按8周计)</t>
         </is>
       </c>
-      <c r="C5" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D5" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E5" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H5" s="32" t="inlineStr">
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" s="35" t="inlineStr">
         <is>
           <t>□ 第7份(必做)</t>
         </is>
       </c>
-      <c r="I5" s="32" t="inlineStr">
+      <c r="I5" s="35" t="inlineStr">
         <is>
           <t>□ 第8份(必做)</t>
         </is>
       </c>
-      <c r="J5" s="34" t="inlineStr">
+      <c r="J5" s="37" t="inlineStr">
         <is>
           <t>三选一:①数练活页卷 ②《5.3全优卷》剩余试卷 ③自备练习卷</t>
         </is>
@@ -5307,12 +5338,12 @@
     </row>
     <row r="6" ht="40" customHeight="1">
       <c r="A6" s="3" t="n"/>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>选做:《教材全解》拓展题 / 与家长商定提高内容</t>
         </is>
       </c>
-      <c r="C6" s="32" t="inlineStr">
+      <c r="C6" s="38" t="inlineStr">
         <is>
           <t>学有余力时安排,不做硬性打卡</t>
         </is>
@@ -5323,62 +5354,62 @@
       <c r="G6" s="5" t="n"/>
       <c r="H6" s="5" t="n"/>
       <c r="I6" s="5" t="n"/>
-      <c r="J6" s="34" t="inlineStr">
+      <c r="J6" s="37" t="inlineStr">
         <is>
           <t>自行安排</t>
         </is>
       </c>
     </row>
     <row r="7" ht="68" customHeight="1">
-      <c r="A7" s="35" t="inlineStr">
+      <c r="A7" s="39" t="inlineStr">
         <is>
           <t>英语</t>
         </is>
       </c>
-      <c r="B7" s="36" t="inlineStr">
+      <c r="B7" s="40" t="inlineStr">
         <is>
           <t>必做④ 学科实践:选3~4首喜爱的古诗,完成A3海报(每次15分钟)</t>
         </is>
       </c>
-      <c r="C7" s="37" t="inlineStr">
+      <c r="C7" s="41" t="inlineStr">
         <is>
           <t>□ 选古诗
 构思</t>
         </is>
       </c>
-      <c r="D7" s="37" t="inlineStr">
+      <c r="D7" s="41" t="inlineStr">
         <is>
           <t>□ 设计
 版面草稿</t>
         </is>
       </c>
-      <c r="E7" s="37" t="inlineStr">
+      <c r="E7" s="41" t="inlineStr">
         <is>
           <t>□ 抄写古诗</t>
         </is>
       </c>
-      <c r="F7" s="37" t="inlineStr">
+      <c r="F7" s="41" t="inlineStr">
         <is>
           <t>□ 配图上色</t>
         </is>
       </c>
-      <c r="G7" s="37" t="inlineStr">
+      <c r="G7" s="41" t="inlineStr">
         <is>
           <t>□ 完善
 落款完成</t>
         </is>
       </c>
-      <c r="H7" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I7" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J7" s="38" t="inlineStr">
+      <c r="H7" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I7" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J7" s="42" t="inlineStr">
         <is>
           <t>共5次;古诗最好是自己学过的中文古诗</t>
         </is>
@@ -5386,64 +5417,64 @@
     </row>
     <row r="8" ht="48" customHeight="1">
       <c r="A8" s="9" t="n"/>
-      <c r="B8" s="36" t="inlineStr">
+      <c r="B8" s="40" t="inlineStr">
         <is>
           <t>选做② 英语试听练习:英文动画电影 / BBC记录片(每次≤10分钟)</t>
         </is>
       </c>
-      <c r="C8" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D8" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="37" t="inlineStr">
+      <c r="C8" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="41" t="inlineStr">
         <is>
           <t>□ ≤10分钟</t>
         </is>
       </c>
-      <c r="F8" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="37" t="inlineStr">
+      <c r="F8" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="41" t="inlineStr">
         <is>
           <t>□ ≤10分钟</t>
         </is>
       </c>
-      <c r="H8" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I8" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J8" s="38" t="inlineStr">
+      <c r="H8" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J8" s="42" t="inlineStr">
         <is>
           <t>共2次,内容自选</t>
         </is>
       </c>
     </row>
     <row r="9" ht="192" customHeight="1">
-      <c r="A9" s="39" t="inlineStr">
+      <c r="A9" s="43" t="inlineStr">
         <is>
           <t>体育</t>
         </is>
       </c>
-      <c r="B9" s="40" t="inlineStr">
+      <c r="B9" s="44" t="inlineStr">
         <is>
           <t>每日锻炼(先热身 → 练习 → 放松拉伸)</t>
         </is>
       </c>
-      <c r="C9" s="41" t="inlineStr">
+      <c r="C9" s="44" t="inlineStr">
         <is>
           <t>□ 热身
 □ 1分钟计时跳绳×4组
@@ -5451,7 +5482,7 @@
 □ 坐位体前屈拉伸1分钟</t>
         </is>
       </c>
-      <c r="D9" s="41" t="inlineStr">
+      <c r="D9" s="44" t="inlineStr">
         <is>
           <t>□ 热身
 □ 跳绳200个/组×4组
@@ -5460,7 +5491,7 @@
 □ 坐位体前屈1分钟</t>
         </is>
       </c>
-      <c r="E9" s="41" t="inlineStr">
+      <c r="E9" s="44" t="inlineStr">
         <is>
           <t>□ 热身
 □ 1分钟计时跳绳×4组
@@ -5469,7 +5500,7 @@
 □ 放松拉伸</t>
         </is>
       </c>
-      <c r="F9" s="41" t="inlineStr">
+      <c r="F9" s="44" t="inlineStr">
         <is>
           <t>□ 热身
 □ 3分钟耐力跳绳
@@ -5477,7 +5508,7 @@
 □ 放松拉伸</t>
         </is>
       </c>
-      <c r="G9" s="41" t="inlineStr">
+      <c r="G9" s="44" t="inlineStr">
         <is>
           <t>□ 热身
 □ 耐力跑2公里
@@ -5486,17 +5517,17 @@
 □ 放松拉伸</t>
         </is>
       </c>
-      <c r="H9" s="33" t="inlineStr">
+      <c r="H9" s="45" t="inlineStr">
         <is>
           <t>休息 · 自由活动</t>
         </is>
       </c>
-      <c r="I9" s="33" t="inlineStr">
+      <c r="I9" s="45" t="inlineStr">
         <is>
           <t>休息 · 自由活动</t>
         </is>
       </c>
-      <c r="J9" s="42" t="inlineStr">
+      <c r="J9" s="46" t="inlineStr">
         <is>
           <t>目标:跳绳200个/分钟;仰卧起坐49个/分钟;体前屈膝盖伸直、手指过脚尖;有条件可加练加速跑</t>
         </is>
@@ -5504,47 +5535,47 @@
     </row>
     <row r="10" ht="52" customHeight="1">
       <c r="A10" s="15" t="n"/>
-      <c r="B10" s="40" t="inlineStr">
+      <c r="B10" s="44" t="inlineStr">
         <is>
           <t>成绩记录(把当天成绩写进括号)</t>
         </is>
       </c>
-      <c r="C10" s="41" t="inlineStr">
+      <c r="C10" s="47" t="inlineStr">
         <is>
           <t>(        )</t>
         </is>
       </c>
-      <c r="D10" s="41" t="inlineStr">
+      <c r="D10" s="47" t="inlineStr">
         <is>
           <t>(        )</t>
         </is>
       </c>
-      <c r="E10" s="41" t="inlineStr">
+      <c r="E10" s="47" t="inlineStr">
         <is>
           <t>(        )</t>
         </is>
       </c>
-      <c r="F10" s="41" t="inlineStr">
+      <c r="F10" s="47" t="inlineStr">
         <is>
           <t>(        )</t>
         </is>
       </c>
-      <c r="G10" s="41" t="inlineStr">
+      <c r="G10" s="47" t="inlineStr">
         <is>
           <t>(        )</t>
         </is>
       </c>
-      <c r="H10" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I10" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J10" s="42" t="inlineStr">
+      <c r="H10" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I10" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J10" s="46" t="inlineStr">
         <is>
           <t>开学交任务单,学校按完成情况评优体奖章</t>
         </is>
@@ -5552,39 +5583,39 @@
     </row>
     <row r="11" ht="52" customHeight="1">
       <c r="A11" s="15" t="n"/>
-      <c r="B11" s="43" t="inlineStr">
+      <c r="B11" s="48" t="inlineStr">
         <is>
           <t>家长点评签字(每周一次)</t>
         </is>
       </c>
-      <c r="C11" s="44" t="inlineStr"/>
-      <c r="D11" s="44" t="n"/>
-      <c r="E11" s="44" t="n"/>
-      <c r="F11" s="44" t="n"/>
-      <c r="G11" s="44" t="n"/>
-      <c r="H11" s="44" t="n"/>
-      <c r="I11" s="44" t="n"/>
-      <c r="J11" s="42" t="inlineStr">
+      <c r="C11" s="49" t="inlineStr"/>
+      <c r="D11" s="49" t="n"/>
+      <c r="E11" s="49" t="n"/>
+      <c r="F11" s="49" t="n"/>
+      <c r="G11" s="49" t="n"/>
+      <c r="H11" s="49" t="n"/>
+      <c r="I11" s="49" t="n"/>
+      <c r="J11" s="46" t="inlineStr">
         <is>
           <t>对应任务单“家长点评签字”栏</t>
         </is>
       </c>
     </row>
     <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="45" t="inlineStr">
+      <c r="A12" s="50" t="inlineStr">
         <is>
           <t>★ 本周是体育任务单最后一周,周末把“注明”栏填好:跳绳最好成绩、跑步公里数及用时、仰卧起坐最好成绩 · 英语必做已全部排完,下周一(8月31日)填自评单</t>
         </is>
       </c>
-      <c r="B12" s="46" t="n"/>
-      <c r="C12" s="46" t="n"/>
-      <c r="D12" s="46" t="n"/>
-      <c r="E12" s="46" t="n"/>
-      <c r="F12" s="46" t="n"/>
-      <c r="G12" s="46" t="n"/>
-      <c r="H12" s="46" t="n"/>
-      <c r="I12" s="46" t="n"/>
-      <c r="J12" s="46" t="n"/>
+      <c r="B12" s="51" t="n"/>
+      <c r="C12" s="51" t="n"/>
+      <c r="D12" s="51" t="n"/>
+      <c r="E12" s="51" t="n"/>
+      <c r="F12" s="51" t="n"/>
+      <c r="G12" s="51" t="n"/>
+      <c r="H12" s="51" t="n"/>
+      <c r="I12" s="51" t="n"/>
+      <c r="J12" s="51" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -5626,165 +5657,165 @@
       </c>
     </row>
     <row r="2" ht="52" customHeight="1">
-      <c r="A2" s="50" t="inlineStr">
+      <c r="A2" s="55" t="inlineStr">
         <is>
           <t>8月31日(周一)当日安排</t>
         </is>
       </c>
-      <c r="B2" s="51" t="n"/>
-      <c r="C2" s="52" t="inlineStr">
+      <c r="B2" s="56" t="n"/>
+      <c r="C2" s="57" t="inlineStr">
         <is>
           <t>开学上交材料清单(装进书包!)</t>
         </is>
       </c>
-      <c r="D2" s="53" t="n"/>
+      <c r="D2" s="58" t="n"/>
     </row>
     <row r="3" ht="68" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="59" t="inlineStr">
         <is>
           <t>数学</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="60" t="inlineStr">
         <is>
           <t>□ 口算15~20道 + 计算4道(最后一组)</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="60" t="inlineStr">
         <is>
           <t>数学 | □ 综合练习卷 8 份(活页卷/《5.3全优卷》/自备)</t>
         </is>
       </c>
-      <c r="D3" s="54" t="n"/>
+      <c r="D3" s="61" t="n"/>
     </row>
     <row r="4" ht="68" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="59" t="inlineStr">
         <is>
           <t>数学</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="60" t="inlineStr">
         <is>
           <t>□ 清点综合练习卷:必做共8份是否完成、订正</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="60" t="inlineStr">
         <is>
           <t>数学 | □ 口算、计算练习记录</t>
         </is>
       </c>
-      <c r="D4" s="54" t="n"/>
+      <c r="D4" s="61" t="n"/>
     </row>
     <row r="5" ht="68" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="59" t="inlineStr">
         <is>
           <t>数学</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="60" t="inlineStr">
         <is>
           <t>□ 检查2项实践作业(A4纸、配照片或表格)</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="60" t="inlineStr">
         <is>
           <t>数学 | □ 实践性作业 2 项(A4纸,自设计格式,配照片或表格)</t>
         </is>
       </c>
-      <c r="D5" s="54" t="n"/>
+      <c r="D5" s="61" t="n"/>
     </row>
     <row r="6" ht="68" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="62" t="inlineStr">
         <is>
           <t>英语</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="63" t="inlineStr">
         <is>
           <t>□ 填写《暑假英语学习自评单》:班级、姓名,勾选2道“是/否”,写下学期英语课的想法和建议</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="63" t="inlineStr">
         <is>
           <t>英语 | □ 《暑假英语学习自评单》(开学报到第一天上交)</t>
         </is>
       </c>
-      <c r="D6" s="54" t="n"/>
+      <c r="D6" s="61" t="n"/>
     </row>
     <row r="7" ht="68" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="62" t="inlineStr">
         <is>
           <t>英语</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="63" t="inlineStr">
         <is>
           <t>□ 检查A3古诗海报、抄写造句和阅读题是否齐全</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="63" t="inlineStr">
         <is>
           <t>英语 | □ A3古诗海报作品(学科实践活动)</t>
         </is>
       </c>
-      <c r="D7" s="54" t="n"/>
+      <c r="D7" s="61" t="n"/>
     </row>
     <row r="8" ht="68" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="32" t="inlineStr">
         <is>
           <t>体育</t>
         </is>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="64" t="inlineStr">
         <is>
           <t>□ 自由锻炼30分钟(跳绳/慢跑,注意防暑)</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="63" t="inlineStr">
         <is>
           <t>英语 | □ 单词抄写造句本、英语阅读题</t>
         </is>
       </c>
-      <c r="D8" s="54" t="n"/>
+      <c r="D8" s="61" t="n"/>
     </row>
     <row r="9" ht="68" customHeight="1">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>体育</t>
         </is>
       </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B9" s="64" t="inlineStr">
         <is>
           <t>□ 体育任务单“注明”栏:填跳绳最好成绩、跑步公里数及用时、仰卧起坐最好成绩;7周家长点评签字补齐</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr">
+      <c r="C9" s="64" t="inlineStr">
         <is>
           <t>体育 | □ 体育家庭任务单(成绩记录+家长点评签字+最好成绩注明)</t>
         </is>
       </c>
-      <c r="D9" s="54" t="n"/>
+      <c r="D9" s="61" t="n"/>
     </row>
     <row r="10" ht="68" customHeight="1">
-      <c r="A10" s="55" t="inlineStr">
+      <c r="A10" s="65" t="inlineStr">
         <is>
           <t>整理</t>
         </is>
       </c>
-      <c r="B10" s="56" t="inlineStr">
+      <c r="B10" s="66" t="inlineStr">
         <is>
           <t>□ 收拾书包文具,调整作息,早睡早起迎接开学</t>
         </is>
       </c>
-      <c r="C10" s="56" t="inlineStr">
+      <c r="C10" s="66" t="inlineStr">
         <is>
           <t>其他 | □ 学校/班级另行通知的材料</t>
         </is>
       </c>
-      <c r="D10" s="54" t="n"/>
+      <c r="D10" s="61" t="n"/>
     </row>
     <row r="11" ht="56" customHeight="1">
-      <c r="A11" s="57" t="inlineStr">
+      <c r="A11" s="50" t="inlineStr">
         <is>
           <t>★ 8月29日(周六)、30日(周日)属于第7周页:综合练习卷第7、8份安排在这两天。如有未完成项目,利用这三天全部补齐!</t>
         </is>
